--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-66.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.7%</t>
+          <t>454.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-497.3%</t>
+          <t>-496.6%</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-143.3%</t>
+          <t>-143.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.7%</t>
+          <t>-135.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-121.7%</t>
+          <t>-127.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-21.0%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.271386310930943</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.5301667585713479</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.806097392953492</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.095085754342682</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-9.146807654593351</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.4791961514802519</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.806097392953492</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.096224898898741</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-9.199702942637638</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.4977204925358589</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.801142046865046</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.101831880713916</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-9.127569767349756</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.4631335181820702</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.801142046865046</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.107565584952552</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-9.056203374740109</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.4443242235320763</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729775654255398</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.140648158124476</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.962744340754885</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.416824091250894</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729775654255398</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.130764676811569</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.695502539886487</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.3117619314029088</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729775654255398</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.128930116312195</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.597595501209996</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.2728994309057735</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.661789904394842</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.169421251255068</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.573641960234038</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.2626495083698965</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.637836363418884</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.184461881986136</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.309582021911242</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.1702858492025299</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.373776425096088</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.329637528818061</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.602502398406403</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1097589665391046</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.373776425096088</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.32685049515776</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.562318100040213</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.1261763097734221</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.333592126729897</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.351304698065317</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.39891822910085</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.190903079369924</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.170192255790535</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.448711441849691</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.165437006871252</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.2922199970996155</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9367110335609361</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.596724604025303</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-7.015770615863737</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3491943431896627</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8438075423184002</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.649574488457865</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.88349514223285</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.3974720193890442</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7115320686875135</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.724307259383424</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.727756809673108</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.4625824131005776</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5557937361277719</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.820565319606906</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.478757010989527</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.5750886737976688</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5557937361277719</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.833471660830564</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.584347000762632</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4048767482892082</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6613837259008764</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.642141737367483</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.603081902881229</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.4459271293188558</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6669797355610076</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.687328473448491</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.45514186147363</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.385224223193728</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.6466588196524501</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.579642100305457</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.402172339219641</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.3976980458418451</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.602709827404373</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.358623932448951</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4081567964550281</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.595749215309279</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.325260725970182</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.4359644334276789</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.610211569690422</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.21700158884766</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.4738002087358826</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.604743690149617</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-6.093710454030529</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.5206147566733117</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4703981625813307</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.676216465050473</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-6.072561255127086</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.5367754144720145</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4492489636778874</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.696606962629864</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.828795813143642</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.630062299612443</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4492489636778874</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.692387670976915</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.727032992866347</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.6728917416433768</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4360298952854587</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.702443425932388</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.477182598917272</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.7655739742067089</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4360298952854587</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.69518550091609</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.30129050644984</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.8395299347143301</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4360298952854587</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.698784624436739</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-5.129844043427377</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>0.9214360259778696</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2645834322629955</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.81498000830477</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-5.055554477689038</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>0.9501723298895022</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1902938665246562</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.858574225364071</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.991918735455103</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>0.9803214278373931</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1266581242907217</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.901450471758749</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.880491976129183</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.006086390351557</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1266581242907217</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.882644730542545</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.640061479324323</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.104001665698378</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1137723725141386</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.028646105250338</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.567818911153128</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.136828006801676</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1137723725141386</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.032575419085158</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.51482058887174</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.158705919631571</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1691086315160774</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.066455758403662</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.406015703392013</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.199225945043456</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1691086315160774</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.063453829623655</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-4.185994905355003</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.288813301268874</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3103284765840577</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.149764773675057</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-4.053127216291725</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.357854559696009</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3103284765840577</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.16565895647688</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.932954132927226</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.40706963748211</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.4305015599485566</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.238908650935882</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.788281987827489</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.475026598083445</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.575173705048294</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.335800040557164</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.848156815185181</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.437114158541794</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5152988776906019</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.285912635543975</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.728336584274344</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.500331420140337</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5152988776906019</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.301201804778183</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.73080629073615</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.406987736878056</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.5128291712287958</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.207364180223541</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.799176477060159</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.298901523833754</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.132191461130572</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.812964529907206</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.283823011326826</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.122628169762463</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.843957689235912</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.096135312635731</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>2.94733773480285</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.668483429443442</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.170892248544507</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>2.951904966794638</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.779419682084691</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.102259776249214</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>2.927646995555845</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.745756136612409</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.044263507839577</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5557684157372926</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.876383436240663</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.685903517408686</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.078376941953198</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5557684157372926</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.886555822672796</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.599660054382309</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.107820597737609</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5557684157372926</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.881502093246656</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.644966873781288</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.081473645422543</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5149582527280618</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.848791770885643</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.67399997848359</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.070412276574724</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5149582527280618</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.849343643918745</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.581189497032731</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.036809161046433</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.6077687341789212</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.834302624680626</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.625578966362158</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.020926849239263</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.5633792648494935</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.80954241900757</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.512907748125908</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.061071045045486</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6760504830857437</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.872220858461043</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.400530746943236</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.111513141349223</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6760504830857437</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.87771215429171</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.428311144844589</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.11189818395722</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.6482700851843906</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.872541117319438</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.268526552422384</v>
+        <v>-3.546691817574727</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.014167740926756</v>
+        <v>0.9029016348658183</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5810522330334144</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.706294955026883</v>
+        <v>2.670566126029505</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.377140630865715</v>
+        <v>-3.655305896018058</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.090871770268629</v>
+        <v>0.9796056642076914</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5810522330334144</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.826444615746089</v>
+        <v>2.790715786748711</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.341731592617572</v>
+        <v>-3.619896857769915</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.119548411670209</v>
+        <v>1.008282305609272</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5810522330334144</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.840957641848412</v>
+        <v>2.805228812851034</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.303347930059421</v>
+        <v>-3.581513195211764</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.132321318035838</v>
+        <v>1.021055211974901</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.678983943920529</v>
+        <v>0.6194358955915655</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.861407280725671</v>
+        <v>2.825678451728293</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.126231600024255</v>
+        <v>-3.404396865176598</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.199896878895206</v>
+        <v>1.088630772834269</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.678983943920529</v>
+        <v>0.6194358955915655</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.858136309570973</v>
+        <v>2.822407480573595</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.171323844857801</v>
+        <v>-3.449489110010144</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.182543372723701</v>
+        <v>1.071277266662764</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6170879007511392</v>
+        <v>0.5575398524221757</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.821682075431252</v>
+        <v>2.785953246433874</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.991948423619033</v>
+        <v>-3.270113688771376</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.248080516525623</v>
+        <v>1.136814410464685</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7738646589218579</v>
+        <v>0.7143166105928944</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.909535105640098</v>
+        <v>2.87380627664272</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.036962637139639</v>
+        <v>-3.315127902291982</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.21088228644897</v>
+        <v>1.099616180388033</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7435157636072532</v>
+        <v>0.6839677152782898</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.872133223782925</v>
+        <v>2.836404394785547</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.303967147412075</v>
+        <v>-3.582132412564418</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.109772044678941</v>
+        <v>0.9985059386180042</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5491527255643047</v>
+        <v>0.4896046772353413</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.761206963296102</v>
+        <v>2.725478134298724</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.405164928849247</v>
+        <v>-3.683330194001591</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.068496854000574</v>
+        <v>0.9572307479396365</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4211958636900221</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.719365597065412</v>
+        <v>2.683636768068034</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.398653962234935</v>
+        <v>-3.676819227387278</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.068701202200615</v>
+        <v>0.9574350961396783</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4211958636900221</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.716965558619728</v>
+        <v>2.68123672962235</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.379615834527637</v>
+        <v>-3.657781099679981</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.072841172491779</v>
+        <v>0.961575066430842</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3630122523588276</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.678580111029257</v>
+        <v>2.642851282031879</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.410742465678255</v>
+        <v>-3.688907730830599</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.237972388970213</v>
+        <v>1.126706282909276</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3630122523588276</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.856161979967937</v>
+        <v>2.820433150970559</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.424609227012173</v>
+        <v>-3.702774492164516</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.233259013422779</v>
+        <v>1.121992907361842</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.3251543356250046</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.834280558913777</v>
+        <v>2.798551729916399</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.379805055472243</v>
+        <v>-3.657970320624586</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.257189212435677</v>
+        <v>1.14592310637474</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.3251543356250046</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.840289089310703</v>
+        <v>2.804560260313325</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.232062085237241</v>
+        <v>-3.510227350389584</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.214236621806878</v>
+        <v>1.10297051574594</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4929616928598878</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.838923724928832</v>
+        <v>2.803194895931454</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.334076767768462</v>
+        <v>-3.612242032920805</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.17622437032587</v>
+        <v>1.064958264264933</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4929616928598878</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.841717346460313</v>
+        <v>2.805988517462935</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.327924061715677</v>
+        <v>-3.606089326868021</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.179347801138642</v>
+        <v>1.068081695077705</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5586624472416355</v>
+        <v>0.4991143989126721</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.846071318483642</v>
+        <v>2.810342489486264</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.344733359866179</v>
+        <v>-3.622898625018522</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.171704558618552</v>
+        <v>1.060438452557615</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4823051007621704</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.835066216333451</v>
+        <v>2.799337387336073</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.282435361090057</v>
+        <v>-3.5606006262424</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.262959311925822</v>
+        <v>1.151693205864884</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4823051007621704</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.901401770130272</v>
+        <v>2.865672941132894</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.080645163424899</v>
+        <v>-3.358810428577242</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.145967392706012</v>
+        <v>1.034701286645074</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7398713412602882</v>
+        <v>0.6803232929313248</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.822504687145892</v>
+        <v>2.786775858148514</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.915832160346052</v>
+        <v>-3.193997425498395</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.282182826259726</v>
+        <v>1.170916720198789</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9046843443391351</v>
+        <v>0.8451362960101717</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.991682721315375</v>
+        <v>2.955953892317997</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.013572704971026</v>
+        <v>-3.29173797012337</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.25771434452578</v>
+        <v>1.146448238464842</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.888795066206155</v>
+        <v>0.8292470178771916</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.996776890551631</v>
+        <v>2.961048061554253</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.189910465093956</v>
+        <v>-3.468075730246299</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.18571522130128</v>
+        <v>1.074449115240342</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6529092577542621</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.889510215302545</v>
+        <v>2.853781386305167</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.113488418662029</v>
+        <v>-3.391653683814372</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.214775657913979</v>
+        <v>1.103509551853042</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6529092577542621</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.888001833342473</v>
+        <v>2.852273004345095</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.06911528702346</v>
+        <v>-3.347280552175803</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.232387778004843</v>
+        <v>1.121121671943905</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6972823893928307</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.914488579761051</v>
+        <v>2.878759750763673</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.946281066136293</v>
+        <v>-3.224446331288636</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.2759152604983</v>
+        <v>1.164649154437363</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6972823893928307</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.908882373899641</v>
+        <v>2.873153544902263</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.898625335575237</v>
+        <v>-3.17679060072758</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.301359309750527</v>
+        <v>1.19009320368959</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8044861682828498</v>
+        <v>0.7449381199538864</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.943857569264079</v>
+        <v>2.908128740266701</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.798107177076482</v>
+        <v>-3.076272442228825</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.346458946524754</v>
+        <v>1.235192840463816</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9050043267816044</v>
+        <v>0.8454562784526409</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.009060837738057</v>
+        <v>2.973332008740678</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.858773767478871</v>
+        <v>-3.136939032631215</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.30894698283967</v>
+        <v>1.197680876778733</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8233060100630707</v>
+        <v>0.7637579617341073</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.946796520182809</v>
+        <v>2.911067691185431</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.813935365870473</v>
+        <v>-3.092100631022817</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.330980046093658</v>
+        <v>1.219713940032721</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8278494430079402</v>
+        <v>0.7683013946789767</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.953620282560359</v>
+        <v>2.917891453562981</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.833433822112482</v>
+        <v>-3.111599087264825</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.327341603227933</v>
+        <v>1.216075497166996</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7797648017280359</v>
+        <v>0.7202167533990724</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.928930437423495</v>
+        <v>2.893201608426117</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.789230985026581</v>
+        <v>-3.067396250178924</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.35090234059013</v>
+        <v>1.239636234529193</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8239676388139363</v>
+        <v>0.7644195904849729</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.961331742202872</v>
+        <v>2.925602913205494</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.826210012690024</v>
+        <v>-3.104375277842367</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.334520729994001</v>
+        <v>1.223254623933063</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.8013934922763034</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.981926083746918</v>
+        <v>2.94619725474954</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.667918595150752</v>
+        <v>-2.946083860303095</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.449085062192749</v>
+        <v>1.337818956131812</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.8013934922763034</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.033173848929958</v>
+        <v>2.99744501993258</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.460276591516276</v>
+        <v>-2.738441856668619</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.530582568240793</v>
+        <v>1.419316462179855</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.068583544239743</v>
+        <v>1.009035495910779</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.156199755704896</v>
+        <v>3.120470926707518</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.409244498793748</v>
+        <v>-2.687409763946091</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.545943633568074</v>
+        <v>1.434677527507137</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.119615636962271</v>
+        <v>1.060067588633308</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.181767239576683</v>
+        <v>3.146038410579305</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.344020317666542</v>
+        <v>-2.622185582818886</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.589220710111661</v>
+        <v>1.477954604050724</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.184839818089477</v>
+        <v>1.125291769760513</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.238089152345712</v>
+        <v>3.202360323348334</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.306593297595409</v>
+        <v>-2.584758562747752</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.600152490439395</v>
+        <v>1.488886384378458</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.190091356118658</v>
+        <v>1.130543307789695</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.237201047462501</v>
+        <v>3.201472218465123</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.326704953630117</v>
+        <v>-2.60487021878246</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.593364620356752</v>
+        <v>1.482098514295815</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.201118701116078</v>
+        <v>1.141570652787114</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.245074246792193</v>
+        <v>3.209345417794815</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.272960139202912</v>
+        <v>-2.551125404355255</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.775420317148845</v>
+        <v>1.664154211087907</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.21118201055654</v>
+        <v>1.151633962227576</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.41167000347768</v>
+        <v>3.375941174480302</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.1981778781779</v>
+        <v>-2.476343143330243</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.925446130776667</v>
+        <v>1.814180024715729</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.285964271581552</v>
+        <v>1.226416223252589</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.576652269310506</v>
+        <v>3.540923440313128</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.172093793914092</v>
+        <v>-2.450259059066435</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.927587740496049</v>
+        <v>1.816321634435112</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.285964271581552</v>
+        <v>1.226416223252589</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.568360245324365</v>
+        <v>3.532631416326987</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.093962613065145</v>
+        <v>-2.372127878217488</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.957033408419407</v>
+        <v>1.84576730235847</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360141082465237</v>
+        <v>1.300593034136273</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.611059527438355</v>
+        <v>3.575330698440977</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.085070151671862</v>
+        <v>-2.363235416824205</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.978144798703512</v>
+        <v>1.866878692642574</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360141082465237</v>
+        <v>1.300593034136273</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.628613933165146</v>
+        <v>3.592885104167768</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.25354626864174</v>
+        <v>-2.531711533794083</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.902609399320145</v>
+        <v>1.791343293259207</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332193246748656</v>
+        <v>1.272645198419693</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.603700279139781</v>
+        <v>3.567971450142403</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.555746739780156</v>
+        <v>-1.8339120049325</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.16299890805264</v>
+        <v>2.051732801991702</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.261845187378245</v>
+        <v>1.202297139049282</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.542761140705397</v>
+        <v>3.507032311708019</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.533025636097004</v>
+        <v>-1.811190901249347</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.162751372022805</v>
+        <v>2.051485265961868</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.261845187378245</v>
+        <v>1.202297139049282</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533425163202302</v>
+        <v>3.497696334204924</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.53130059280696</v>
+        <v>-1.809465857959303</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.322347515189992</v>
+        <v>2.211081409129054</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.263570230668289</v>
+        <v>1.204022182339326</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.693366315027497</v>
+        <v>3.657637486030119</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.686081599585215</v>
+        <v>-1.964246864737559</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.297512934972336</v>
+        <v>2.186246828911399</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.230202556613813</v>
+        <v>1.17065450828485</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.710423533088457</v>
+        <v>3.674694704091079</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.679026909370042</v>
+        <v>-1.957192174522385</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.297010167047951</v>
+        <v>2.185744060987013</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.237257246828987</v>
+        <v>1.177709198500023</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.711331703207107</v>
+        <v>3.675602874209729</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.652075685043554</v>
+        <v>-1.930240950195897</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.317796810423288</v>
+        <v>2.206530704362351</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.252137592856706</v>
+        <v>1.192589544527743</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.73026606446848</v>
+        <v>3.694537235471102</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.78802869309987</v>
+        <v>-2.066193958252213</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.447518739345721</v>
+        <v>2.336252633284784</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.252137592856706</v>
+        <v>1.192589544527743</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.91436919661344</v>
+        <v>3.878640367616062</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.810436810904742</v>
+        <v>-2.088602076057085</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.430672187126765</v>
+        <v>2.319406081065828</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.252137592856706</v>
+        <v>1.192589544527743</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.906485891516433</v>
+        <v>3.870757062519055</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.958442578384141</v>
+        <v>-2.236607843536484</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.373523879684643</v>
+        <v>2.262257773623706</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165410583993165</v>
+        <v>1.105862535664201</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.856503685747946</v>
+        <v>3.820774856750567</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.967883504272671</v>
+        <v>-2.246048769425014</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.426001227051078</v>
+        <v>2.314735120990141</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287837701536556</v>
+        <v>1.228289653207593</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.986213673995827</v>
+        <v>3.950484844998449</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.020157111608312</v>
+        <v>-2.298322376760656</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.407982878662123</v>
+        <v>2.296716772601185</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.235564094200915</v>
+        <v>1.176016045871951</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.957740604139744</v>
+        <v>3.922011775142366</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.096487089209218</v>
+        <v>-2.374652354361562</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.375562700515535</v>
+        <v>2.264296594454598</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.235564094200915</v>
+        <v>1.176016045871951</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.955852417033519</v>
+        <v>3.920123588036141</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.208244041824519</v>
+        <v>-2.486409306976863</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.325680149072277</v>
+        <v>2.21441404301134</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.123807141585614</v>
+        <v>1.06425909325665</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.8836184750672</v>
+        <v>3.847889646069822</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.206403022766268</v>
+        <v>-2.484568287918612</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.32485056690573</v>
+        <v>2.213584460844793</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.125075368257082</v>
+        <v>1.065527319928119</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.882813421280234</v>
+        <v>3.847084592282856</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.338704314863821</v>
+        <v>-2.616869580016165</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.285003456932627</v>
+        <v>2.17373735087169</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.125075368257082</v>
+        <v>1.065527319928119</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.895886828146153</v>
+        <v>3.860157999148774</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.340265957678681</v>
+        <v>-2.618431222831025</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.284378799806683</v>
+        <v>2.173112693745746</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.125075368257082</v>
+        <v>1.065527319928119</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.895886828146153</v>
+        <v>3.860157999148774</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.368166744788154</v>
+        <v>-2.646332009940498</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.271742526089896</v>
+        <v>2.160476420028958</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.090478444114147</v>
+        <v>1.030930395785184</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.873652714787394</v>
+        <v>3.837923885790016</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.490692847491048</v>
+        <v>-2.768858112643392</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.219496528985938</v>
+        <v>2.108230422925</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9679523414112534</v>
+        <v>0.90840429308229</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.796901497142856</v>
+        <v>3.761172668145478</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.510754168767555</v>
+        <v>-2.788919433919899</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.278177960065839</v>
+        <v>2.166911854004901</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9478910201347464</v>
+        <v>0.8883429718057829</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.851570663967456</v>
+        <v>3.815841834970078</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.767474986762378</v>
+        <v>-3.045640251914723</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.315801351869756</v>
+        <v>2.204535245808819</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.926833638483013</v>
+        <v>3.891104809485636</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.921461404538519</v>
+        <v>-3.199626669690863</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.32318705390494</v>
+        <v>2.211920947844002</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.995813907628653</v>
+        <v>3.960085078631275</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.870939500710853</v>
+        <v>-3.149104765863197</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.329447017556127</v>
+        <v>2.218180911495189</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.981865109748775</v>
+        <v>3.946136280751396</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.123414654718577</v>
+        <v>-3.401579919870922</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.240327445008451</v>
+        <v>2.129061338947513</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.993735598804188</v>
+        <v>3.95800676980681</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.392887456640286</v>
+        <v>-3.67105272179263</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.133748858758711</v>
+        <v>2.022482752697774</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.994946133323132</v>
+        <v>3.959217304325754</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.550431528369727</v>
+        <v>-3.828596793522071</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.074852972294257</v>
+        <v>1.963586866233319</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7725746408506571</v>
+        <v>0.7130265925216936</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.958926792466289</v>
+        <v>3.923197963468911</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.679282079071773</v>
+        <v>-3.957447344224117</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.018390604749627</v>
+        <v>1.907124498688689</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6720331836709721</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.929408599892046</v>
+        <v>3.893679770894667</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.796249771710664</v>
+        <v>-4.074415036863009</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.133807584393115</v>
+        <v>2.022541478332177</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6720331836709721</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.09161265659109</v>
+        <v>4.055883827593711</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.880967713931618</v>
+        <v>-4.159132979083962</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.094767045468548</v>
+        <v>1.98350093940761</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6464652030718891</v>
+        <v>0.5869171547429257</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.035389677198076</v>
+        <v>3.999660848200698</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.962902532200502</v>
+        <v>-4.241067797352845</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.072222535729485</v>
+        <v>1.960956429668548</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.636530457484809</v>
+        <v>0.5769824091558455</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.039658247414319</v>
+        <v>4.00392941841694</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.909164358800239</v>
+        <v>-4.187329623952583</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.102643443545492</v>
+        <v>1.991377337484555</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6902686308850711</v>
+        <v>0.6307205825561076</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.080826789910379</v>
+        <v>4.045097960913001</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.799158075323017</v>
+        <v>-4.077323340475361</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.138798844180557</v>
+        <v>2.027532738119619</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7134732028023463</v>
+        <v>0.6539251544733828</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.086902420304919</v>
+        <v>4.051173591307541</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.656098499582092</v>
+        <v>-3.934263764734436</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.200272685198901</v>
+        <v>2.089006579137964</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7214866293923256</v>
+        <v>0.6619385810633621</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.095960486980881</v>
+        <v>4.060231657983503</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.354651774110255</v>
+        <v>-3.632817039262599</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.328112258270172</v>
+        <v>2.216846152209235</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9633853065351994</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.284089405146519</v>
+        <v>4.248360576149141</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.409606970553324</v>
+        <v>-3.687772235705668</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.307101357445655</v>
+        <v>2.195835251384718</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9633853065351994</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.28506058289923</v>
+        <v>4.249331753901852</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.730505270579194</v>
+        <v>3.411695024640633</v>
       </c>
       <c r="C2031" t="n">
         <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.35739886000209</v>
+        <v>-3.349959215138914</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.328827506045904</v>
+        <v>2.331803363991174</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9633853065351994</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.285903487278985</v>
+        <v>4.250174658281607</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>49.5%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,22 +992,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.9%</t>
+          <t>457.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-496.6%</t>
+          <t>-509.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-143.0%</t>
+          <t>-148.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.3%</t>
+          <t>-132.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-127.7%</t>
+          <t>-121.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-17.4%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.271386310930943</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5301667585713479</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.806097392953492</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.095085754342682</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.146807654593351</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4791961514802519</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.806097392953492</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.096224898898741</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.199702942637638</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4977204925358589</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.801142046865046</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.101831880713916</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.127569767349756</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4631335181820702</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.801142046865046</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.107565584952552</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.056203374740109</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4443242235320763</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.729775654255398</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.140648158124476</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.962744340754885</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.416824091250894</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.729775654255398</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.130764676811569</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.695502539886487</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3117619314029088</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.729775654255398</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.128930116312195</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.597595501209996</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2728994309057735</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.661789904394842</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.169421251255068</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.573641960234038</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2626495083698965</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.637836363418884</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.184461881986136</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.309582021911242</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1702858492025299</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.373776425096088</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.329637528818061</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.602502398406403</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1097589665391046</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.373776425096088</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.32685049515776</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.562318100040213</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1261763097734221</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.333592126729897</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.351304698065317</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.39891822910085</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.190903079369924</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.170192255790535</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.448711441849691</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.165437006871252</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2922199970996155</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9367110335609361</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.596724604025303</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.015770615863737</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3491943431896627</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8438075423184002</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.649574488457865</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.88349514223285</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3974720193890442</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7115320686875135</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.724307259383424</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.727756809673108</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4625824131005776</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5557937361277719</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.820565319606906</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.478757010989527</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5750886737976688</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5557937361277719</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.833471660830564</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.584347000762632</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4048767482892082</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6613837259008764</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.642141737367483</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.603081902881229</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4459271293188558</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6669797355610076</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.687328473448491</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.45514186147363</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.385224223193728</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6466588196524501</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.579642100305457</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.402172339219641</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3976980458418451</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.602709827404373</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.358623932448951</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4081567964550281</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.595749215309279</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.325260725970182</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4359644334276789</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.610211569690422</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.21700158884766</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4738002087358826</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.604743690149617</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.093710454030529</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5206147566733117</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4703981625813307</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.676216465050473</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.072561255127086</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5367754144720145</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4492489636778874</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.696606962629864</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.828795813143642</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.630062299612443</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4492489636778874</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.692387670976915</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.727032992866347</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6728917416433768</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4360298952854587</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.702443425932388</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.477182598917272</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7655739742067089</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4360298952854587</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.69518550091609</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.30129050644984</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8395299347143301</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4360298952854587</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.698784624436739</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.129844043427377</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9214360259778696</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2645834322629955</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.81498000830477</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055554477689038</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9501723298895022</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1902938665246562</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.858574225364071</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991918735455103</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9803214278373931</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1266581242907217</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.901450471758749</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.880491976129183</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.006086390351557</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1266581242907217</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.882644730542545</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.640061479324323</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.104001665698378</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1137723725141386</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.028646105250338</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.567818911153128</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.136828006801676</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1137723725141386</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.032575419085158</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.51482058887174</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.158705919631571</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1691086315160774</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.066455758403662</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.406015703392013</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.199225945043456</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1691086315160774</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.063453829623655</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.185994905355003</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.288813301268874</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3103284765840577</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.149764773675057</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.053127216291725</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.357854559696009</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3103284765840577</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.16565895647688</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.932954132927226</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.40706963748211</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4305015599485566</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.238908650935882</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.788281987827489</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.475026598083445</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.575173705048294</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.335800040557164</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.848156815185181</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.437114158541794</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5152988776906019</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.285912635543975</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.728336584274344</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.500331420140337</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5152988776906019</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.301201804778183</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.73080629073615</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.406987736878056</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5128291712287958</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.207364180223541</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.799176477060159</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.298901523833754</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.132191461130572</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.812964529907206</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.283823011326826</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.122628169762463</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.843957689235912</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.096135312635731</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.94733773480285</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.668483429443442</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.170892248544507</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.951904966794638</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.779419682084691</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.102259776249214</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.927646995555845</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.745756136612409</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.044263507839577</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5557684157372926</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.876383436240663</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.685903517408686</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.078376941953198</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5557684157372926</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.886555822672796</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.599660054382309</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.107820597737609</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5557684157372926</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.881502093246656</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.644966873781288</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.081473645422543</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5149582527280618</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.848791770885643</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.67399997848359</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.070412276574724</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5149582527280618</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.849343643918745</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.581189497032731</v>
+        <v>-3.303024231880388</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.036809161046433</v>
+        <v>1.148075267107371</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6077687341789212</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.834302624680626</v>
+        <v>2.870031453678004</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.625578966362158</v>
+        <v>-3.347413701209815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.020926849239263</v>
+        <v>1.132192955300201</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5633792648494935</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.80954241900757</v>
+        <v>2.845271248004948</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.512907748125908</v>
+        <v>-3.234742482973565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.061071045045486</v>
+        <v>1.172337151106424</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6760504830857437</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.872220858461043</v>
+        <v>2.907949687458421</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.400530746943236</v>
+        <v>-3.122365481790892</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.111513141349223</v>
+        <v>1.22277924741016</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6760504830857437</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.87771215429171</v>
+        <v>2.913440983289088</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.428311144844589</v>
+        <v>-3.150145879692245</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.11189818395722</v>
+        <v>1.223164290018158</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6482700851843906</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.872541117319438</v>
+        <v>2.908269946316816</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.546691817574727</v>
+        <v>-3.268526552422384</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9029016348658183</v>
+        <v>1.014167740926756</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5810522330334144</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.670566126029505</v>
+        <v>2.706294955026883</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.655305896018058</v>
+        <v>-3.377140630865715</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9796056642076914</v>
+        <v>1.090871770268629</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5810522330334144</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.790715786748711</v>
+        <v>2.826444615746089</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.619896857769915</v>
+        <v>-3.341731592617572</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.008282305609272</v>
+        <v>1.119548411670209</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5810522330334144</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.805228812851034</v>
+        <v>2.840957641848412</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.581513195211764</v>
+        <v>-3.303347930059421</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.021055211974901</v>
+        <v>1.132321318035838</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6194358955915655</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.825678451728293</v>
+        <v>2.861407280725671</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.404396865176598</v>
+        <v>-3.126231600024255</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.088630772834269</v>
+        <v>1.199896878895206</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6194358955915655</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.822407480573595</v>
+        <v>2.858136309570973</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.449489110010144</v>
+        <v>-3.171323844857801</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.071277266662764</v>
+        <v>1.182543372723701</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5575398524221757</v>
+        <v>0.6170879007511392</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.785953246433874</v>
+        <v>2.821682075431252</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.270113688771376</v>
+        <v>-2.991948423619033</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.136814410464685</v>
+        <v>1.248080516525623</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7143166105928944</v>
+        <v>0.7738646589218579</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.87380627664272</v>
+        <v>2.909535105640098</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.315127902291982</v>
+        <v>-3.036962637139639</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.099616180388033</v>
+        <v>1.21088228644897</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6839677152782898</v>
+        <v>0.7435157636072532</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.836404394785547</v>
+        <v>2.872133223782925</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.582132412564418</v>
+        <v>-3.303967147412075</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9985059386180042</v>
+        <v>1.109772044678941</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4896046772353413</v>
+        <v>0.5491527255643047</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.725478134298724</v>
+        <v>2.761206963296102</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.683330194001591</v>
+        <v>-3.405164928849247</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9572307479396365</v>
+        <v>1.068496854000574</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4211958636900221</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.683636768068034</v>
+        <v>2.719365597065412</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.676819227387278</v>
+        <v>-3.398653962234935</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9574350961396783</v>
+        <v>1.068701202200615</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4211958636900221</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.68123672962235</v>
+        <v>2.716965558619728</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.657781099679981</v>
+        <v>-3.379615834527637</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.961575066430842</v>
+        <v>1.072841172491779</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3630122523588276</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.642851282031879</v>
+        <v>2.678580111029257</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.688907730830599</v>
+        <v>-3.410742465678255</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.126706282909276</v>
+        <v>1.237972388970213</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3630122523588276</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.820433150970559</v>
+        <v>2.856161979967937</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.702774492164516</v>
+        <v>-3.424609227012173</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.121992907361842</v>
+        <v>1.233259013422779</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3251543356250046</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.798551729916399</v>
+        <v>2.834280558913777</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.657970320624586</v>
+        <v>-3.503508657483288</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.14592310637474</v>
+        <v>1.207707771631259</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3251543356250046</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.804560260313325</v>
+        <v>2.840289089310703</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.510227350389584</v>
+        <v>-3.355765687248286</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.10297051574594</v>
+        <v>1.16475518100246</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4929616928598878</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.803194895931454</v>
+        <v>2.838923724928832</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.612242032920805</v>
+        <v>-3.457780369779507</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.064958264264933</v>
+        <v>1.126742929521452</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4929616928598878</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.805988517462935</v>
+        <v>2.841717346460313</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.606089326868021</v>
+        <v>-3.451627663726722</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.068081695077705</v>
+        <v>1.129866360334224</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4991143989126721</v>
+        <v>0.5586624472416355</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.810342489486264</v>
+        <v>2.846071318483642</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.622898625018522</v>
+        <v>-3.468436961877224</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.060438452557615</v>
+        <v>1.122223117814134</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4823051007621704</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.799337387336073</v>
+        <v>2.835066216333451</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.5606006262424</v>
+        <v>-3.406138963101102</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.151693205864884</v>
+        <v>1.213477871121404</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4823051007621704</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.865672941132894</v>
+        <v>2.901401770130272</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.358810428577242</v>
+        <v>-3.204348765435944</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.034701286645074</v>
+        <v>1.096485951901594</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6803232929313248</v>
+        <v>0.7398713412602882</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.786775858148514</v>
+        <v>2.822504687145892</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.193997425498395</v>
+        <v>-3.039535762357097</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.170916720198789</v>
+        <v>1.232701385455308</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8451362960101717</v>
+        <v>0.9046843443391351</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.955953892317997</v>
+        <v>2.991682721315375</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.29173797012337</v>
+        <v>-3.137276306982071</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.146448238464842</v>
+        <v>1.208232903721362</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8292470178771916</v>
+        <v>0.888795066206155</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.961048061554253</v>
+        <v>2.996776890551631</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.468075730246299</v>
+        <v>-3.313614067105001</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.074449115240342</v>
+        <v>1.136233780496862</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6529092577542621</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.853781386305167</v>
+        <v>2.889510215302545</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.391653683814372</v>
+        <v>-3.237192020673074</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.103509551853042</v>
+        <v>1.165294217109561</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6529092577542621</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.852273004345095</v>
+        <v>2.888001833342473</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.347280552175803</v>
+        <v>-3.192818889034505</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.121121671943905</v>
+        <v>1.182906337200425</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6972823893928307</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.878759750763673</v>
+        <v>2.914488579761051</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.224446331288636</v>
+        <v>-3.069984668147338</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.164649154437363</v>
+        <v>1.226433819693882</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6972823893928307</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.873153544902263</v>
+        <v>2.908882373899641</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.17679060072758</v>
+        <v>-3.022328937586282</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.19009320368959</v>
+        <v>1.251877868946109</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7449381199538864</v>
+        <v>0.8044861682828498</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.908128740266701</v>
+        <v>2.943857569264079</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.076272442228825</v>
+        <v>-2.921810779087528</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.235192840463816</v>
+        <v>1.296977505720336</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8454562784526409</v>
+        <v>0.9050043267816044</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.973332008740678</v>
+        <v>3.009060837738057</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.136939032631215</v>
+        <v>-2.982477369489917</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.197680876778733</v>
+        <v>1.259465542035252</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7637579617341073</v>
+        <v>0.8233060100630707</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.911067691185431</v>
+        <v>2.946796520182809</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.092100631022817</v>
+        <v>-2.937638967881519</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.219713940032721</v>
+        <v>1.28149860528924</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7683013946789767</v>
+        <v>0.8278494430079402</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.917891453562981</v>
+        <v>2.953620282560359</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.111599087264825</v>
+        <v>-2.957137424123527</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.216075497166996</v>
+        <v>1.277860162423515</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7202167533990724</v>
+        <v>0.7797648017280359</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.893201608426117</v>
+        <v>2.928930437423495</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.067396250178924</v>
+        <v>-2.912934587037626</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.239636234529193</v>
+        <v>1.301420899785712</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7644195904849729</v>
+        <v>0.8239676388139363</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.925602913205494</v>
+        <v>2.961331742202872</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.104375277842367</v>
+        <v>-2.94991361470107</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.223254623933063</v>
+        <v>1.285039289189582</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8013934922763034</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.94619725474954</v>
+        <v>2.981926083746918</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.946083860303095</v>
+        <v>-2.791622197161797</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.337818956131812</v>
+        <v>1.399603621388331</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8013934922763034</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.99744501993258</v>
+        <v>3.033173848929958</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.738441856668619</v>
+        <v>-2.583980193527321</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.419316462179855</v>
+        <v>1.481101127436375</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.009035495910779</v>
+        <v>1.068583544239743</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.120470926707518</v>
+        <v>3.156199755704896</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.687409763946091</v>
+        <v>-2.532948100804793</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.434677527507137</v>
+        <v>1.496462192763656</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.060067588633308</v>
+        <v>1.119615636962271</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.146038410579305</v>
+        <v>3.181767239576683</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.622185582818886</v>
+        <v>-2.467723919677588</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.477954604050724</v>
+        <v>1.539739269307243</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.125291769760513</v>
+        <v>1.184839818089477</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.202360323348334</v>
+        <v>3.238089152345712</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.584758562747752</v>
+        <v>-2.430296899606454</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.488886384378458</v>
+        <v>1.550671049634977</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.130543307789695</v>
+        <v>1.190091356118658</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.201472218465123</v>
+        <v>3.237201047462501</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.60487021878246</v>
+        <v>-2.450408555641162</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.482098514295815</v>
+        <v>1.543883179552334</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.141570652787114</v>
+        <v>1.201118701116078</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.209345417794815</v>
+        <v>3.245074246792193</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.551125404355255</v>
+        <v>-2.396663741213958</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.664154211087907</v>
+        <v>1.725938876344426</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.151633962227576</v>
+        <v>1.21118201055654</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.375941174480302</v>
+        <v>3.41167000347768</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.476343143330243</v>
+        <v>-2.321881480188945</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.814180024715729</v>
+        <v>1.875964689972249</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.226416223252589</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.540923440313128</v>
+        <v>3.576652269310506</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.450259059066435</v>
+        <v>-2.295797395925137</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.816321634435112</v>
+        <v>1.878106299691631</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.226416223252589</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.532631416326987</v>
+        <v>3.568360245324365</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.372127878217488</v>
+        <v>-2.21766621507619</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.84576730235847</v>
+        <v>1.907551967614989</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.300593034136273</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.575330698440977</v>
+        <v>3.611059527438355</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.363235416824205</v>
+        <v>-2.208773753682907</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.866878692642574</v>
+        <v>1.928663357899094</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.300593034136273</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.592885104167768</v>
+        <v>3.628613933165146</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.531711533794083</v>
+        <v>-2.377249870652785</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.791343293259207</v>
+        <v>1.853127958515727</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.272645198419693</v>
+        <v>1.332193246748656</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.567971450142403</v>
+        <v>3.603700279139781</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.8339120049325</v>
+        <v>-1.679450341791202</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.051732801991702</v>
+        <v>2.113517467248221</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.202297139049282</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.507032311708019</v>
+        <v>3.542761140705397</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.811190901249347</v>
+        <v>-1.656729238108049</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.051485265961868</v>
+        <v>2.113269931218387</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.202297139049282</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.497696334204924</v>
+        <v>3.533425163202302</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.809465857959303</v>
+        <v>-1.655004194818005</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.211081409129054</v>
+        <v>2.272866074385574</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.204022182339326</v>
+        <v>1.263570230668289</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.657637486030119</v>
+        <v>3.693366315027497</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.964246864737559</v>
+        <v>-1.809785201596261</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.186246828911399</v>
+        <v>2.248031494167918</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.17065450828485</v>
+        <v>1.230202556613813</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.674694704091079</v>
+        <v>3.710423533088457</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.957192174522385</v>
+        <v>-1.802730511381087</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.185744060987013</v>
+        <v>2.247528726243533</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.177709198500023</v>
+        <v>1.237257246828987</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.675602874209729</v>
+        <v>3.711331703207107</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.930240950195897</v>
+        <v>-1.775779287054599</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.206530704362351</v>
+        <v>2.26831536961887</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.192589544527743</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.694537235471102</v>
+        <v>3.73026606446848</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.066193958252213</v>
+        <v>-1.911732295110915</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.336252633284784</v>
+        <v>2.398037298541303</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.192589544527743</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.878640367616062</v>
+        <v>3.91436919661344</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.088602076057085</v>
+        <v>-1.934140412915787</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.319406081065828</v>
+        <v>2.381190746322347</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.192589544527743</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.870757062519055</v>
+        <v>3.906485891516433</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.236607843536484</v>
+        <v>-2.082146180395187</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.262257773623706</v>
+        <v>2.324042438880225</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.105862535664201</v>
+        <v>1.165410583993165</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.820774856750567</v>
+        <v>3.856503685747946</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.246048769425014</v>
+        <v>-2.091587106283717</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.314735120990141</v>
+        <v>2.37651978624666</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.228289653207593</v>
+        <v>1.287837701536556</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.950484844998449</v>
+        <v>3.986213673995827</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.298322376760656</v>
+        <v>-2.143860713619358</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.296716772601185</v>
+        <v>2.358501437857704</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.176016045871951</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.922011775142366</v>
+        <v>3.957740604139744</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.374652354361562</v>
+        <v>-2.220190691220264</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.264296594454598</v>
+        <v>2.326081259711117</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.176016045871951</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.920123588036141</v>
+        <v>3.955852417033519</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.486409306976863</v>
+        <v>-2.331947643835565</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.21441404301134</v>
+        <v>2.276198708267859</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.06425909325665</v>
+        <v>1.123807141585614</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.847889646069822</v>
+        <v>3.8836184750672</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.484568287918612</v>
+        <v>-2.330106624777314</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.213584460844793</v>
+        <v>2.275369126101312</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.065527319928119</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.847084592282856</v>
+        <v>3.882813421280234</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.616869580016165</v>
+        <v>-2.462407916874867</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.17373735087169</v>
+        <v>2.235522016128209</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.065527319928119</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.860157999148774</v>
+        <v>3.895886828146153</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.618431222831025</v>
+        <v>-2.463969559689727</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.173112693745746</v>
+        <v>2.234897359002265</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.065527319928119</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.860157999148774</v>
+        <v>3.895886828146153</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.646332009940498</v>
+        <v>-2.4918703467992</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.160476420028958</v>
+        <v>2.222261085285478</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.030930395785184</v>
+        <v>1.090478444114147</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.837923885790016</v>
+        <v>3.873652714787394</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.768858112643392</v>
+        <v>-2.614396449502094</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.108230422925</v>
+        <v>2.170015088181519</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.90840429308229</v>
+        <v>0.9679523414112534</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.761172668145478</v>
+        <v>3.796901497142856</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.788919433919899</v>
+        <v>-2.634457770778601</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.166911854004901</v>
+        <v>2.22869651926142</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8883429718057829</v>
+        <v>0.9478910201347464</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.815841834970078</v>
+        <v>3.851570663967456</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.045640251914723</v>
+        <v>-2.891178588773425</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.204535245808819</v>
+        <v>2.266319911065337</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.891104809485636</v>
+        <v>3.926833638483013</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.199626669690863</v>
+        <v>-3.045165006549565</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.211920947844002</v>
+        <v>2.273705613100521</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.960085078631275</v>
+        <v>3.995813907628653</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.149104765863197</v>
+        <v>-2.994643102721899</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.218180911495189</v>
+        <v>2.279965576751708</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.946136280751396</v>
+        <v>3.981865109748775</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.401579919870922</v>
+        <v>-3.247118256729624</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.129061338947513</v>
+        <v>2.190846004204032</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.95800676980681</v>
+        <v>3.993735598804188</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.67105272179263</v>
+        <v>-3.516591058651332</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.022482752697774</v>
+        <v>2.084267417954293</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.959217304325754</v>
+        <v>3.994946133323132</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.828596793522071</v>
+        <v>-3.674135130380773</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.963586866233319</v>
+        <v>2.025371531489838</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7130265925216936</v>
+        <v>0.7725746408506571</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.923197963468911</v>
+        <v>3.958926792466289</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.957447344224117</v>
+        <v>-3.80298568108282</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.907124498688689</v>
+        <v>1.968909163945209</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6720331836709721</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.893679770894667</v>
+        <v>3.929408599892046</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.074415036863009</v>
+        <v>-3.91995337372171</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.022541478332177</v>
+        <v>2.084326143588696</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6720331836709721</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.055883827593711</v>
+        <v>4.09161265659109</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.159132979083962</v>
+        <v>-4.004671315942664</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.98350093940761</v>
+        <v>2.045285604664129</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5869171547429257</v>
+        <v>0.6464652030718891</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.999660848200698</v>
+        <v>4.035389677198076</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.241067797352845</v>
+        <v>-4.086606134211547</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.960956429668548</v>
+        <v>2.022741094925067</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5769824091558455</v>
+        <v>0.636530457484809</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.00392941841694</v>
+        <v>4.039658247414319</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.187329623952583</v>
+        <v>-4.032867960811285</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.991377337484555</v>
+        <v>2.053162002741074</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6307205825561076</v>
+        <v>0.6902686308850711</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.045097960913001</v>
+        <v>4.080826789910379</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.077323340475361</v>
+        <v>-3.922861677334064</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.027532738119619</v>
+        <v>2.089317403376138</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6539251544733828</v>
+        <v>0.7134732028023463</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.051173591307541</v>
+        <v>4.086902420304919</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.934263764734436</v>
+        <v>-3.779802101593138</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.089006579137964</v>
+        <v>2.150791244394483</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.6619385810633621</v>
+        <v>0.7214866293923256</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.060231657983503</v>
+        <v>4.095960486980881</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.632817039262599</v>
+        <v>-3.478355376121301</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.216846152209235</v>
+        <v>2.278630817465753</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9633853065351994</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.248360576149141</v>
+        <v>4.284089405146519</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.687772235705668</v>
+        <v>-3.53331057256437</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.195835251384718</v>
+        <v>2.257619916641237</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9633853065351994</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.249331753901852</v>
+        <v>4.28506058289923</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.411695024640633</v>
+        <v>3.775737696031882</v>
       </c>
       <c r="C2031" t="n">
         <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.349959215138914</v>
+        <v>-3.48227219655785</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.331803363991174</v>
+        <v>2.2788781714236</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.9633853065351994</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.250174658281607</v>
+        <v>4.285903487278985</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808528</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>49.1%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-68.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>457.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-509.8%</t>
+          <t>-537.1%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.3%</t>
+          <t>-159.3%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.0%</t>
+          <t>-130.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-121.7%</t>
+          <t>-127.7%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-86.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2031"/>
+  <dimension ref="A1:G2032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.271386310930943</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.5301667585713479</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.806097392953492</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.095085754342682</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-9.146807654593351</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.4791961514802519</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.806097392953492</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.096224898898741</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-9.199702942637638</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.4977204925358589</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.801142046865046</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.101831880713916</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-9.127569767349756</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.4631335181820702</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.801142046865046</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.107565584952552</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-9.056203374740109</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.4443242235320763</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729775654255398</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.140648158124476</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.962744340754885</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.416824091250894</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729775654255398</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.130764676811569</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.695502539886487</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.3117619314029088</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729775654255398</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.128930116312195</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.597595501209996</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.2728994309057735</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.661789904394842</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.169421251255068</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.573641960234038</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.2626495083698965</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.637836363418884</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.184461881986136</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.309582021911242</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.1702858492025299</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.373776425096088</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.329637528818061</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.602502398406403</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1097589665391046</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.373776425096088</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.32685049515776</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.562318100040213</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.1261763097734221</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.333592126729897</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.351304698065317</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.39891822910085</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.190903079369924</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.170192255790535</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.448711441849691</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.165437006871252</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.2922199970996155</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9367110335609361</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.596724604025303</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-7.015770615863737</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3491943431896627</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8438075423184002</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.649574488457865</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.88349514223285</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.3974720193890442</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7115320686875135</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.724307259383424</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.727756809673108</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.4625824131005776</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5557937361277719</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.820565319606906</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.478757010989527</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.5750886737976688</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5557937361277719</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.833471660830564</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.584347000762632</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4048767482892082</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6613837259008764</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.642141737367483</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.603081902881229</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.4459271293188558</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6669797355610076</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.687328473448491</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.45514186147363</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.385224223193728</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.6466588196524501</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.579642100305457</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.402172339219641</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.3976980458418451</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.602709827404373</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.358623932448951</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4081567964550281</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.595749215309279</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.325260725970182</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.4359644334276789</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.610211569690422</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.21700158884766</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.4738002087358826</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5936892973984612</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.604743690149617</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-6.093710454030529</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.5206147566733117</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4703981625813307</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.676216465050473</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-6.072561255127086</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.5367754144720145</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4492489636778874</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.696606962629864</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.828795813143642</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.630062299612443</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4492489636778874</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.692387670976915</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.727032992866347</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.6728917416433768</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4360298952854587</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.702443425932388</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.477182598917272</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.7655739742067089</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4360298952854587</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.69518550091609</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.30129050644984</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.8395299347143301</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4360298952854587</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.698784624436739</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-5.129844043427377</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>0.9214360259778696</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2645834322629955</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.81498000830477</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-5.055554477689038</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>0.9501723298895022</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1902938665246562</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.858574225364071</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.991918735455103</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>0.9803214278373931</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1266581242907217</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.901450471758749</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.880491976129183</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.006086390351557</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1266581242907217</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.882644730542545</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.640061479324323</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.104001665698378</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1137723725141386</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.028646105250338</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.567818911153128</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.136828006801676</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1137723725141386</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.032575419085158</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.51482058887174</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.158705919631571</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1691086315160774</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.066455758403662</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.406015703392013</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.199225945043456</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1691086315160774</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.063453829623655</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-4.185994905355003</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.288813301268874</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3103284765840577</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.149764773675057</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-4.053127216291725</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.357854559696009</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3103284765840577</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.16565895647688</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.932954132927226</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.40706963748211</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.4305015599485566</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.238908650935882</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.788281987827489</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.475026598083445</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.575173705048294</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.335800040557164</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.848156815185181</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.437114158541794</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5152988776906019</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.285912635543975</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.728336584274344</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.500331420140337</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5152988776906019</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.301201804778183</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.73080629073615</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.406987736878056</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.5128291712287958</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.207364180223541</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.799176477060159</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.298901523833754</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.132191461130572</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.812964529907206</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.283823011326826</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.122628169762463</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.843957689235912</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.096135312635731</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>2.94733773480285</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.668483429443442</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.170892248544507</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>2.951904966794638</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.779419682084691</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.102259776249214</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5221048702650107</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>2.927646995555845</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.745756136612409</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.044263507839577</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5557684157372926</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.876383436240663</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.685903517408686</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.078376941953198</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5557684157372926</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.886555822672796</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.599660054382309</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.107820597737609</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5557684157372926</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.881502093246656</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.644966873781288</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.081473645422543</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5149582527280618</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.848791770885643</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.67399997848359</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.070412276574724</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5149582527280618</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.849343643918745</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.581189497032731</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.036809161046433</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.6077687341789212</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.834302624680626</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.625578966362158</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.020926849239263</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.5633792648494935</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.80954241900757</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.512907748125908</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.061071045045486</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6760504830857437</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.872220858461043</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.400530746943236</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.111513141349223</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6760504830857437</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.87771215429171</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.428311144844589</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.11189818395722</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.6482700851843906</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.872541117319438</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.268526552422384</v>
+        <v>-3.546691817574727</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.014167740926756</v>
+        <v>0.9029016348658183</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5810522330334144</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.706294955026883</v>
+        <v>2.670566126029505</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.377140630865715</v>
+        <v>-3.655305896018058</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.090871770268629</v>
+        <v>0.9796056642076914</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5810522330334144</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.826444615746089</v>
+        <v>2.790715786748711</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.341731592617572</v>
+        <v>-3.619896857769915</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.119548411670209</v>
+        <v>1.008282305609272</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.5810522330334144</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.840957641848412</v>
+        <v>2.805228812851034</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.303347930059421</v>
+        <v>-3.581513195211764</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.132321318035838</v>
+        <v>1.021055211974901</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.678983943920529</v>
+        <v>0.6194358955915655</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.861407280725671</v>
+        <v>2.825678451728293</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.126231600024255</v>
+        <v>-3.404396865176598</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.199896878895206</v>
+        <v>1.088630772834269</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.678983943920529</v>
+        <v>0.6194358955915655</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.858136309570973</v>
+        <v>2.822407480573595</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.171323844857801</v>
+        <v>-3.449489110010144</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.182543372723701</v>
+        <v>1.071277266662764</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6170879007511392</v>
+        <v>0.5575398524221757</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.821682075431252</v>
+        <v>2.785953246433874</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.991948423619033</v>
+        <v>-3.270113688771376</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.248080516525623</v>
+        <v>1.136814410464685</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7738646589218579</v>
+        <v>0.7143166105928944</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.909535105640098</v>
+        <v>2.87380627664272</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.036962637139639</v>
+        <v>-3.315127902291982</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.21088228644897</v>
+        <v>1.099616180388033</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7435157636072532</v>
+        <v>0.6839677152782898</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.872133223782925</v>
+        <v>2.836404394785547</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.303967147412075</v>
+        <v>-3.582132412564418</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.109772044678941</v>
+        <v>0.9985059386180042</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5491527255643047</v>
+        <v>0.4896046772353413</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.761206963296102</v>
+        <v>2.725478134298724</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.405164928849247</v>
+        <v>-3.683330194001591</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.068496854000574</v>
+        <v>0.9572307479396365</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4211958636900221</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.719365597065412</v>
+        <v>2.683636768068034</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.398653962234935</v>
+        <v>-3.676819227387278</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.068701202200615</v>
+        <v>0.9574350961396783</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4211958636900221</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.716965558619728</v>
+        <v>2.68123672962235</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.379615834527637</v>
+        <v>-3.657781099679981</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.072841172491779</v>
+        <v>0.961575066430842</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3630122523588276</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.678580111029257</v>
+        <v>2.642851282031879</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.410742465678255</v>
+        <v>-3.688907730830599</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.237972388970213</v>
+        <v>1.126706282909276</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.422560300687791</v>
+        <v>0.3630122523588276</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.856161979967937</v>
+        <v>2.820433150970559</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.424609227012173</v>
+        <v>-3.702774492164516</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.233259013422779</v>
+        <v>1.121992907361842</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.3251543356250046</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.834280558913777</v>
+        <v>2.798551729916399</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.503508657483288</v>
+        <v>-3.77671463877603</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.207707771631259</v>
+        <v>1.098425379114162</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.3251543356250046</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.840289089310703</v>
+        <v>2.804560260313325</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.355765687248286</v>
+        <v>-3.628971668541027</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.16475518100246</v>
+        <v>1.055472788485363</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4929616928598878</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.838923724928832</v>
+        <v>2.803194895931454</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.457780369779507</v>
+        <v>-3.730986351072248</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.126742929521452</v>
+        <v>1.017460537004355</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4929616928598878</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.841717346460313</v>
+        <v>2.805988517462935</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.451627663726722</v>
+        <v>-3.724833645019464</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.129866360334224</v>
+        <v>1.020583967817128</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5586624472416355</v>
+        <v>0.4991143989126721</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.846071318483642</v>
+        <v>2.810342489486264</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.468436961877224</v>
+        <v>-3.741642943169965</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.122223117814134</v>
+        <v>1.012940725297037</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4823051007621704</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.835066216333451</v>
+        <v>2.799337387336073</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.406138963101102</v>
+        <v>-3.679344944393844</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.213477871121404</v>
+        <v>1.104195478604307</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4823051007621704</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.901401770130272</v>
+        <v>2.865672941132894</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.204348765435944</v>
+        <v>-3.477554746728686</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.096485951901594</v>
+        <v>0.9872035593844972</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7398713412602882</v>
+        <v>0.6803232929313248</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.822504687145892</v>
+        <v>2.786775858148514</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.039535762357097</v>
+        <v>-3.312741743649839</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.232701385455308</v>
+        <v>1.123418992938211</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9046843443391351</v>
+        <v>0.8451362960101717</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.991682721315375</v>
+        <v>2.955953892317997</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.137276306982071</v>
+        <v>-3.410482288274813</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.208232903721362</v>
+        <v>1.098950511204265</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.888795066206155</v>
+        <v>0.8292470178771916</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.996776890551631</v>
+        <v>2.961048061554253</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.313614067105001</v>
+        <v>-3.586820048397742</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.136233780496862</v>
+        <v>1.026951387979765</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6529092577542621</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.889510215302545</v>
+        <v>2.853781386305167</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.237192020673074</v>
+        <v>-3.510398001965815</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.165294217109561</v>
+        <v>1.056011824592464</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.6529092577542621</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.888001833342473</v>
+        <v>2.852273004345095</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.192818889034505</v>
+        <v>-3.466024870327247</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.182906337200425</v>
+        <v>1.073623944683328</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6972823893928307</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.914488579761051</v>
+        <v>2.878759750763673</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.069984668147338</v>
+        <v>-3.343190649440079</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.226433819693882</v>
+        <v>1.117151427176786</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6972823893928307</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.908882373899641</v>
+        <v>2.873153544902263</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.022328937586282</v>
+        <v>-3.295534918879024</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.251877868946109</v>
+        <v>1.142595476429012</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8044861682828498</v>
+        <v>0.7449381199538864</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.943857569264079</v>
+        <v>2.908128740266701</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.921810779087528</v>
+        <v>-3.195016760380269</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.296977505720336</v>
+        <v>1.187695113203239</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9050043267816044</v>
+        <v>0.8454562784526409</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.009060837738057</v>
+        <v>2.973332008740678</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.982477369489917</v>
+        <v>-3.255683350782658</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.259465542035252</v>
+        <v>1.150183149518156</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8233060100630707</v>
+        <v>0.7637579617341073</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.946796520182809</v>
+        <v>2.911067691185431</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.937638967881519</v>
+        <v>-3.21084494917426</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.28149860528924</v>
+        <v>1.172216212772144</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8278494430079402</v>
+        <v>0.7683013946789767</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.953620282560359</v>
+        <v>2.917891453562981</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.957137424123527</v>
+        <v>-3.230343405416268</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.277860162423515</v>
+        <v>1.168577769906418</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7797648017280359</v>
+        <v>0.7202167533990724</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.928930437423495</v>
+        <v>2.893201608426117</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.912934587037626</v>
+        <v>-3.186140568330368</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.301420899785712</v>
+        <v>1.192138507268615</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8239676388139363</v>
+        <v>0.7644195904849729</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.961331742202872</v>
+        <v>2.925602913205494</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.94991361470107</v>
+        <v>-3.223119595993811</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.285039289189582</v>
+        <v>1.175756896672486</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.8013934922763034</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.981926083746918</v>
+        <v>2.94619725474954</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.791622197161797</v>
+        <v>-3.064828178454539</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.399603621388331</v>
+        <v>1.290321228871234</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.8013934922763034</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.033173848929958</v>
+        <v>2.99744501993258</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.583980193527321</v>
+        <v>-2.857186174820062</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.481101127436375</v>
+        <v>1.371818734919278</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.068583544239743</v>
+        <v>1.009035495910779</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.156199755704896</v>
+        <v>3.120470926707518</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.532948100804793</v>
+        <v>-2.806154082097534</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.496462192763656</v>
+        <v>1.387179800246559</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.119615636962271</v>
+        <v>1.060067588633308</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.181767239576683</v>
+        <v>3.146038410579305</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.467723919677588</v>
+        <v>-2.740929900970329</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.539739269307243</v>
+        <v>1.430456876790146</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.184839818089477</v>
+        <v>1.125291769760513</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.238089152345712</v>
+        <v>3.202360323348334</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.430296899606454</v>
+        <v>-2.703502880899195</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.550671049634977</v>
+        <v>1.44138865711788</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.190091356118658</v>
+        <v>1.130543307789695</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.237201047462501</v>
+        <v>3.201472218465123</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.450408555641162</v>
+        <v>-2.723614536933904</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.543883179552334</v>
+        <v>1.434600787035237</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.201118701116078</v>
+        <v>1.141570652787114</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.245074246792193</v>
+        <v>3.209345417794815</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.396663741213958</v>
+        <v>-2.669869722506699</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.725938876344426</v>
+        <v>1.61665648382733</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.21118201055654</v>
+        <v>1.151633962227576</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.41167000347768</v>
+        <v>3.375941174480302</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.321881480188945</v>
+        <v>-2.595087461481686</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.875964689972249</v>
+        <v>1.766682297455152</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.285964271581552</v>
+        <v>1.226416223252589</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.576652269310506</v>
+        <v>3.540923440313128</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.295797395925137</v>
+        <v>-2.569003377217878</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.878106299691631</v>
+        <v>1.768823907174534</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.285964271581552</v>
+        <v>1.226416223252589</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.568360245324365</v>
+        <v>3.532631416326987</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.21766621507619</v>
+        <v>-2.490872196368931</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.907551967614989</v>
+        <v>1.798269575097893</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360141082465237</v>
+        <v>1.300593034136273</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.611059527438355</v>
+        <v>3.575330698440977</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.208773753682907</v>
+        <v>-2.481979734975648</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.928663357899094</v>
+        <v>1.819380965381997</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360141082465237</v>
+        <v>1.300593034136273</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.628613933165146</v>
+        <v>3.592885104167768</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.377249870652785</v>
+        <v>-2.650455851945526</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.853127958515727</v>
+        <v>1.74384556599863</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332193246748656</v>
+        <v>1.272645198419693</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.603700279139781</v>
+        <v>3.567971450142403</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.679450341791202</v>
+        <v>-1.952656323083943</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.113517467248221</v>
+        <v>2.004235074731125</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.261845187378245</v>
+        <v>1.202297139049282</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.542761140705397</v>
+        <v>3.507032311708019</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.656729238108049</v>
+        <v>-1.92993521940079</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.113269931218387</v>
+        <v>2.003987538701291</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.261845187378245</v>
+        <v>1.202297139049282</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533425163202302</v>
+        <v>3.497696334204924</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.655004194818005</v>
+        <v>-1.928210176110747</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.272866074385574</v>
+        <v>2.163583681868477</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.263570230668289</v>
+        <v>1.204022182339326</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.693366315027497</v>
+        <v>3.657637486030119</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.809785201596261</v>
+        <v>-2.082991182889002</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.248031494167918</v>
+        <v>2.138749101650822</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.230202556613813</v>
+        <v>1.17065450828485</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.710423533088457</v>
+        <v>3.674694704091079</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.802730511381087</v>
+        <v>-2.075936492673828</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.247528726243533</v>
+        <v>2.138246333726436</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.237257246828987</v>
+        <v>1.177709198500023</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.711331703207107</v>
+        <v>3.675602874209729</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.775779287054599</v>
+        <v>-2.04898526834734</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.26831536961887</v>
+        <v>2.159032977101773</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.252137592856706</v>
+        <v>1.192589544527743</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.73026606446848</v>
+        <v>3.694537235471102</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.911732295110915</v>
+        <v>-2.184938276403656</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.398037298541303</v>
+        <v>2.288754906024206</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.252137592856706</v>
+        <v>1.192589544527743</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.91436919661344</v>
+        <v>3.878640367616062</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.934140412915787</v>
+        <v>-2.207346394208528</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.381190746322347</v>
+        <v>2.271908353805251</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.252137592856706</v>
+        <v>1.192589544527743</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.906485891516433</v>
+        <v>3.870757062519055</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.082146180395187</v>
+        <v>-2.355352161687928</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.324042438880225</v>
+        <v>2.214760046363128</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165410583993165</v>
+        <v>1.105862535664201</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.856503685747946</v>
+        <v>3.820774856750567</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.091587106283717</v>
+        <v>-2.364793087576458</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.37651978624666</v>
+        <v>2.267237393729563</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287837701536556</v>
+        <v>1.228289653207593</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.986213673995827</v>
+        <v>3.950484844998449</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.143860713619358</v>
+        <v>-2.417066694912099</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.358501437857704</v>
+        <v>2.249219045340608</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.235564094200915</v>
+        <v>1.176016045871951</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.957740604139744</v>
+        <v>3.922011775142366</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.220190691220264</v>
+        <v>-2.493396672513005</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.326081259711117</v>
+        <v>2.21679886719402</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.235564094200915</v>
+        <v>1.176016045871951</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.955852417033519</v>
+        <v>3.920123588036141</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.331947643835565</v>
+        <v>-2.605153625128306</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.276198708267859</v>
+        <v>2.166916315750762</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.123807141585614</v>
+        <v>1.06425909325665</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.8836184750672</v>
+        <v>3.847889646069822</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.330106624777314</v>
+        <v>-2.603312606070055</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.275369126101312</v>
+        <v>2.166086733584216</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.125075368257082</v>
+        <v>1.065527319928119</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.882813421280234</v>
+        <v>3.847084592282856</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.462407916874867</v>
+        <v>-2.735613898167608</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.235522016128209</v>
+        <v>2.126239623611113</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.125075368257082</v>
+        <v>1.065527319928119</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.895886828146153</v>
+        <v>3.860157999148774</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.463969559689727</v>
+        <v>-2.737175540982468</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.234897359002265</v>
+        <v>2.125614966485168</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.125075368257082</v>
+        <v>1.065527319928119</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.895886828146153</v>
+        <v>3.860157999148774</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.4918703467992</v>
+        <v>-2.765076328091941</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.222261085285478</v>
+        <v>2.112978692768381</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.090478444114147</v>
+        <v>1.030930395785184</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.873652714787394</v>
+        <v>3.837923885790016</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.614396449502094</v>
+        <v>-2.887602430794835</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.170015088181519</v>
+        <v>2.060732695664423</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9679523414112534</v>
+        <v>0.90840429308229</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.796901497142856</v>
+        <v>3.761172668145478</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.634457770778601</v>
+        <v>-2.907663752071342</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.22869651926142</v>
+        <v>2.119414126744323</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9478910201347464</v>
+        <v>0.8883429718057829</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.851570663967456</v>
+        <v>3.815841834970078</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.891178588773425</v>
+        <v>-3.164384570066166</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.266319911065337</v>
+        <v>2.157037518548241</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.926833638483013</v>
+        <v>3.891104809485636</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.045165006549565</v>
+        <v>-3.318370987842306</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.273705613100521</v>
+        <v>2.164423220583425</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.995813907628653</v>
+        <v>3.960085078631275</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808528</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.994643102721899</v>
+        <v>-3.267849084014641</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.279965576751708</v>
+        <v>2.170683184234612</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.981865109748775</v>
+        <v>3.946136280751396</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.247118256729624</v>
+        <v>-3.520324238022365</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.190846004204032</v>
+        <v>2.081563611686936</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.993735598804188</v>
+        <v>3.95800676980681</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.516591058651332</v>
+        <v>-3.789797039944073</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.084267417954293</v>
+        <v>1.974985025437197</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7799283976619681</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.994946133323132</v>
+        <v>3.959217304325754</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.674135130380773</v>
+        <v>-3.947341111673514</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.025371531489838</v>
+        <v>1.916089138972741</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7725746408506571</v>
+        <v>0.7130265925216936</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.958926792466289</v>
+        <v>3.923197963468911</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.80298568108282</v>
+        <v>-4.07619166237556</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.968909163945209</v>
+        <v>1.859626771428113</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6720331836709721</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.929408599892046</v>
+        <v>3.893679770894667</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.91995337372171</v>
+        <v>-4.193159355014451</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.084326143588696</v>
+        <v>1.9750437510716</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6720331836709721</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.09161265659109</v>
+        <v>4.055883827593711</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.004671315942664</v>
+        <v>-4.277877297235404</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.045285604664129</v>
+        <v>1.936003212147033</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6464652030718891</v>
+        <v>0.5869171547429257</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.035389677198076</v>
+        <v>3.999660848200698</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.086606134211547</v>
+        <v>-4.359812115504288</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.022741094925067</v>
+        <v>1.913458702407971</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.636530457484809</v>
+        <v>0.5769824091558455</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.039658247414319</v>
+        <v>4.00392941841694</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.032867960811285</v>
+        <v>-4.306073942104025</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.053162002741074</v>
+        <v>1.943879610223978</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6902686308850711</v>
+        <v>0.6307205825561076</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.080826789910379</v>
+        <v>4.045097960913001</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.922861677334064</v>
+        <v>-4.196067658626804</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.089317403376138</v>
+        <v>1.980035010859042</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7134732028023463</v>
+        <v>0.6539251544733828</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.086902420304919</v>
+        <v>4.051173591307541</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.779802101593138</v>
+        <v>-4.053008082885878</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.150791244394483</v>
+        <v>2.041508851877387</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7214866293923256</v>
+        <v>0.6619385810633621</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.095960486980881</v>
+        <v>4.060231657983503</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.478355376121301</v>
+        <v>-3.751561357414041</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.278630817465753</v>
+        <v>2.169348424948658</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9633853065351994</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.284089405146519</v>
+        <v>4.248360576149141</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.53331057256437</v>
+        <v>-3.80651655385711</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.257619916641237</v>
+        <v>2.148337524124141</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9633853065351994</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.28506058289923</v>
+        <v>4.249331753901852</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,45 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.775737696031882</v>
+        <v>3.821198342859304</v>
       </c>
       <c r="C2031" t="n">
         <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.48227219655785</v>
+        <v>-3.755478177850589</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.2788781714236</v>
+        <v>2.169595778906504</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9633853065351994</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.285903487278985</v>
+        <v>4.250174658281607</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="2" t="n">
+        <v>45494</v>
+      </c>
+      <c r="B2032" t="n">
+        <v>3.776123010868705</v>
+      </c>
+      <c r="C2032" t="n">
+        <v>3.607663610959577</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>-3.755478177850589</v>
+      </c>
+      <c r="E2032" t="n">
+        <v>2.169595778906504</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>0.9633853065351994</v>
+      </c>
+      <c r="G2032" t="n">
+        <v>3.600727407945945</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-642.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.1%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-537.1%</t>
+          <t>-507.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-257.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.3%</t>
+          <t>-147.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-130.1%</t>
+          <t>-132.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-127.7%</t>
+          <t>-121.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.0%</t>
+          <t>-86.3%</t>
         </is>
       </c>
     </row>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.36434170361416</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.791997431992835</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.614212383628741</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.693818283441618</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-3.820724160515763</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.607319631343068</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.140068235596265</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.481354928011126</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.571874028746052</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.294965498218616</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.806568022878604</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.189372675567685</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.142230670109057</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.05368820833147</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.218675000311928</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>1.029598036484562</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.583802382950675</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.8828015984348951</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-5.992391160131353</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.7181276315773832</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.106151572154218</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.6678088992396978</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.522543446441215</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.4992462001337761</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.766814847168285</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4117963305116272</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-6.972065866405045</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.3257954879626186</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.020268683647389</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.3049192811206818</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.316930025457586</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.1900337203258111</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.503649733766889</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.1113195324676868</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-7.88665112250952</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.04198312435094964</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-7.891137567710909</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.04120618646007523</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.250667890214912</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.179668012163626</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.301016953669134</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.1918916175881371</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.39863623109053</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.2278975779349266</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.452707730598888</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.2466326214166981</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.656965905928752</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.322822694430001</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.690618744437225</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.3318012753489543</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.617148912769776</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.2870416411885537</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.79227333015632</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.3425361873956545</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.026725424170809</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.4435361899030461</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.131100155197256</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.4919582730876009</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.183886310797583</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.5119569454891755</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.309923104165872</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5596779342073765</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.252851332269941</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.5328588897626032</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.394523173994061</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.591002853350993</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.344932329569227</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.5561131054161872</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.19601399509737</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5095969052741274</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.271386310930943</v>
+        <v>-8.970168842377959</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5301667585713479</v>
+        <v>-0.4096797711501541</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.806097392953492</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.095085754342682</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.146807654593351</v>
+        <v>-8.845590186040367</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4791961514802519</v>
+        <v>-0.3587091640590585</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.806097392953492</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.096224898898741</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.199702942637638</v>
+        <v>-8.898485474084653</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4977204925358589</v>
+        <v>-0.3772335051146651</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.801142046865046</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.101831880713916</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.127569767349756</v>
+        <v>-8.826352298796772</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4631335181820702</v>
+        <v>-0.3426465307608764</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.801142046865046</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.107565584952552</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.056203374740109</v>
+        <v>-8.754985906187125</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4443242235320763</v>
+        <v>-0.3238372361108826</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.729775654255398</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.140648158124476</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.962744340754885</v>
+        <v>-8.6615268722019</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.416824091250894</v>
+        <v>-0.2963371038297002</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.729775654255398</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.130764676811569</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.695502539886487</v>
+        <v>-8.394285071333503</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3117619314029088</v>
+        <v>-0.191274943981715</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.729775654255398</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.128930116312195</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.597595501209996</v>
+        <v>-8.296378032657012</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2728994309057735</v>
+        <v>-0.1524124434845797</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.661789904394842</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.169421251255068</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.573641960234038</v>
+        <v>-8.272424491681054</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2626495083698965</v>
+        <v>-0.1421625209487027</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.637836363418884</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.184461881986136</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.309582021911242</v>
+        <v>-8.008364553358259</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1702858492025299</v>
+        <v>-0.04979886178133652</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.373776425096088</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.329637528818061</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.602502398406403</v>
+        <v>-7.301284929853421</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1097589665391046</v>
+        <v>0.2302459539602979</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.373776425096088</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.32685049515776</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.562318100040213</v>
+        <v>-7.26110063148723</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1261763097734221</v>
+        <v>0.2466632971946154</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.333592126729897</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.351304698065317</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.39891822910085</v>
+        <v>-7.097700760547868</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.190903079369924</v>
+        <v>0.3113900667911174</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.170192255790535</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.448711441849691</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.165437006871252</v>
+        <v>-6.864219538318269</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2922199970996155</v>
+        <v>0.4127069845208089</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9367110335609361</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.596724604025303</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.015770615863737</v>
+        <v>-6.714553147310754</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3491943431896627</v>
+        <v>0.469681330610856</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8438075423184002</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.649574488457865</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.88349514223285</v>
+        <v>-6.582277673679868</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3974720193890442</v>
+        <v>0.5179590068102375</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7115320686875135</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.724307259383424</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.727756809673108</v>
+        <v>-6.426539341120126</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4625824131005776</v>
+        <v>0.5830694005217709</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5557937361277719</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.820565319606906</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.478757010989527</v>
+        <v>-6.177539542436545</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5750886737976688</v>
+        <v>0.6955756612188622</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5557937361277719</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.833471660830564</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.584347000762632</v>
+        <v>-6.283129532209649</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4048767482892082</v>
+        <v>0.5253637357104015</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6613837259008764</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.642141737367483</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.603081902881229</v>
+        <v>-6.301864434328246</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4459271293188558</v>
+        <v>0.5664141167400492</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6669797355610076</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.687328473448491</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.45514186147363</v>
+        <v>-6.153924392920647</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.385224223193728</v>
+        <v>0.5057112106149213</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6466588196524501</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.579642100305457</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.402172339219641</v>
+        <v>-6.100954870666659</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3976980458418451</v>
+        <v>0.5181850332630384</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.602709827404373</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.358623932448951</v>
+        <v>-6.057406463895968</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4081567964550281</v>
+        <v>0.5286437838762215</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.595749215309279</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.325260725970182</v>
+        <v>-6.024043257417199</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4359644334276789</v>
+        <v>0.5564514208488722</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.610211569690422</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.21700158884766</v>
+        <v>-5.915784120294678</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4738002087358826</v>
+        <v>0.5942871961570759</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5936892973984612</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.604743690149617</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.093710454030529</v>
+        <v>-5.792492985477547</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5206147566733117</v>
+        <v>0.641101744094505</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4703981625813307</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.676216465050473</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.072561255127086</v>
+        <v>-5.771343786574104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5367754144720145</v>
+        <v>0.6572624018932078</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4492489636778874</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.696606962629864</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.828795813143642</v>
+        <v>-5.527578344590659</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.630062299612443</v>
+        <v>0.7505492870336363</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4492489636778874</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.692387670976915</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.727032992866347</v>
+        <v>-5.425815524313364</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6728917416433768</v>
+        <v>0.7933787290645702</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4360298952854587</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.702443425932388</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.477182598917272</v>
+        <v>-5.17596513036429</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7655739742067089</v>
+        <v>0.8860609616279023</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4360298952854587</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.69518550091609</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.30129050644984</v>
+        <v>-5.000073037896857</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8395299347143301</v>
+        <v>0.9600169221355239</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4360298952854587</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.698784624436739</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.129844043427377</v>
+        <v>-4.828626574874393</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9214360259778696</v>
+        <v>1.041923013399063</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2645834322629955</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.81498000830477</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055554477689038</v>
+        <v>-4.754337009136054</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9501723298895022</v>
+        <v>1.070659317310696</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1902938665246562</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.858574225364071</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991918735455103</v>
+        <v>-4.69070126690212</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9803214278373931</v>
+        <v>1.100808415258587</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1266581242907217</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.901450471758749</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.880491976129183</v>
+        <v>-4.5792745075762</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.006086390351557</v>
+        <v>1.12657337777275</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1266581242907217</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.882644730542545</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.640061479324323</v>
+        <v>-4.338844010771339</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.104001665698378</v>
+        <v>1.224488653119572</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1137723725141386</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.028646105250338</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.567818911153128</v>
+        <v>-4.266601442600145</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.136828006801676</v>
+        <v>1.25731499422287</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1137723725141386</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.032575419085158</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.51482058887174</v>
+        <v>-4.213603120318757</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.158705919631571</v>
+        <v>1.279192907052765</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1691086315160774</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.066455758403662</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.406015703392013</v>
+        <v>-4.10479823483903</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.199225945043456</v>
+        <v>1.319712932464649</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1691086315160774</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.063453829623655</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.185994905355003</v>
+        <v>-3.884777436802019</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.288813301268874</v>
+        <v>1.409300288690068</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3103284765840577</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.149764773675057</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.053127216291725</v>
+        <v>-3.751909747738741</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.357854559696009</v>
+        <v>1.478341547117203</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3103284765840577</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.16565895647688</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.932954132927226</v>
+        <v>-3.631736664374242</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.40706963748211</v>
+        <v>1.527556624903304</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4305015599485566</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.238908650935882</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.788281987827489</v>
+        <v>-3.487064519274504</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.475026598083445</v>
+        <v>1.595513585504639</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.575173705048294</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.335800040557164</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.848156815185181</v>
+        <v>-3.546939346632197</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.437114158541794</v>
+        <v>1.557601145962988</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5152988776906019</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.285912635543975</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.728336584274344</v>
+        <v>-3.427119115721359</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.500331420140337</v>
+        <v>1.620818407561531</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5152988776906019</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.301201804778183</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.73080629073615</v>
+        <v>-3.429588822183165</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.406987736878056</v>
+        <v>1.52747472429925</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5128291712287958</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.207364180223541</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.799176477060159</v>
+        <v>-3.497959008507175</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.298901523833754</v>
+        <v>1.419388511254948</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.132191461130572</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.812964529907206</v>
+        <v>-3.626090800996107</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.283823011326826</v>
+        <v>1.358572502891266</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.122628169762463</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.843957689235912</v>
+        <v>-3.657083960324813</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.096135312635731</v>
+        <v>1.170884804200171</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.94733773480285</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.668483429443442</v>
+        <v>-3.481609700532343</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.170892248544507</v>
+        <v>1.245641740108946</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.951904966794638</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.779419682084691</v>
+        <v>-3.592545953173592</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.102259776249214</v>
+        <v>1.177009267813654</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5221048702650107</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.927646995555845</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.745756136612409</v>
+        <v>-3.55888240770131</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.044263507839577</v>
+        <v>1.119012999404017</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5557684157372926</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.876383436240663</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.685903517408686</v>
+        <v>-3.499029788497587</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.078376941953198</v>
+        <v>1.153126433517638</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5557684157372926</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.886555822672796</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.599660054382309</v>
+        <v>-3.41278632547121</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.107820597737609</v>
+        <v>1.182570089302049</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5557684157372926</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.881502093246656</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.644966873781288</v>
+        <v>-3.458093144870189</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.081473645422543</v>
+        <v>1.156223136986983</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5149582527280618</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.848791770885643</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.67399997848359</v>
+        <v>-3.487126249572491</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.070412276574724</v>
+        <v>1.145161768139164</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5149582527280618</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.849343643918745</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.581189497032731</v>
+        <v>-3.394315768121632</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.036809161046433</v>
+        <v>1.111558652610873</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6077687341789212</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.834302624680626</v>
+        <v>2.870031453678004</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.625578966362158</v>
+        <v>-3.438705237451059</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.020926849239263</v>
+        <v>1.095676340803703</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5633792648494935</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.80954241900757</v>
+        <v>2.845271248004948</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.512907748125908</v>
+        <v>-3.326034019214809</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.061071045045486</v>
+        <v>1.135820536609926</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6760504830857437</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.872220858461043</v>
+        <v>2.907949687458421</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.400530746943236</v>
+        <v>-3.213657018032137</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.111513141349223</v>
+        <v>1.186262632913663</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6760504830857437</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.87771215429171</v>
+        <v>2.913440983289088</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.428311144844589</v>
+        <v>-3.24143741593349</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.11189818395722</v>
+        <v>1.18664767552166</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6482700851843906</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.872541117319438</v>
+        <v>2.908269946316816</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.546691817574727</v>
+        <v>-3.359818088663628</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9029016348658183</v>
+        <v>0.9776511264302581</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5810522330334144</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.670566126029505</v>
+        <v>2.706294955026883</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.655305896018058</v>
+        <v>-3.468432167106959</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9796056642076914</v>
+        <v>1.054355155772131</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5810522330334144</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.790715786748711</v>
+        <v>2.826444615746089</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.619896857769915</v>
+        <v>-3.433023128858816</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.008282305609272</v>
+        <v>1.083031797173712</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5810522330334144</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.805228812851034</v>
+        <v>2.840957641848412</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.581513195211764</v>
+        <v>-3.394639466300665</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.021055211974901</v>
+        <v>1.095804703539341</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6194358955915655</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.825678451728293</v>
+        <v>2.861407280725671</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.404396865176598</v>
+        <v>-3.217523136265499</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.088630772834269</v>
+        <v>1.163380264398709</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6194358955915655</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.822407480573595</v>
+        <v>2.858136309570973</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.449489110010144</v>
+        <v>-3.262615381099045</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.071277266662764</v>
+        <v>1.146026758227204</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5575398524221757</v>
+        <v>0.6170879007511392</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.785953246433874</v>
+        <v>2.821682075431252</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.270113688771376</v>
+        <v>-3.083239959860277</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.136814410464685</v>
+        <v>1.211563902029125</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7143166105928944</v>
+        <v>0.7738646589218579</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.87380627664272</v>
+        <v>2.909535105640098</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.315127902291982</v>
+        <v>-3.128254173380884</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.099616180388033</v>
+        <v>1.174365671952472</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6839677152782898</v>
+        <v>0.7435157636072532</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.836404394785547</v>
+        <v>2.872133223782925</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.582132412564418</v>
+        <v>-3.395258683653319</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9985059386180042</v>
+        <v>1.073255430182444</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4896046772353413</v>
+        <v>0.5491527255643047</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.725478134298724</v>
+        <v>2.761206963296102</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.683330194001591</v>
+        <v>-3.496456465090492</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9572307479396365</v>
+        <v>1.031980239504076</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4211958636900221</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.683636768068034</v>
+        <v>2.719365597065412</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.676819227387278</v>
+        <v>-3.489945498476179</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9574350961396783</v>
+        <v>1.032184587704118</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4211958636900221</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.68123672962235</v>
+        <v>2.716965558619728</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.657781099679981</v>
+        <v>-3.470907370768882</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.961575066430842</v>
+        <v>1.036324557995282</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3630122523588276</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.642851282031879</v>
+        <v>2.678580111029257</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.688907730830599</v>
+        <v>-3.5020340019195</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.126706282909276</v>
+        <v>1.201455774473715</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3630122523588276</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.820433150970559</v>
+        <v>2.856161979967937</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.702774492164516</v>
+        <v>-3.515900763253417</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.121992907361842</v>
+        <v>1.196742398926282</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3251543356250046</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.798551729916399</v>
+        <v>2.834280558913777</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.77671463877603</v>
+        <v>-3.594800193724532</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.098425379114162</v>
+        <v>1.171191157134762</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3251543356250046</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.804560260313325</v>
+        <v>2.840289089310703</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.628971668541027</v>
+        <v>-3.44705722348953</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.055472788485363</v>
+        <v>1.128238566505962</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4929616928598878</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.803194895931454</v>
+        <v>2.838923724928832</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.730986351072248</v>
+        <v>-3.549071906020751</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.017460537004355</v>
+        <v>1.090226315024955</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4929616928598878</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.805988517462935</v>
+        <v>2.841717346460313</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.724833645019464</v>
+        <v>-3.542919199967967</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.020583967817128</v>
+        <v>1.093349745837727</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4991143989126721</v>
+        <v>0.5586624472416355</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.810342489486264</v>
+        <v>2.846071318483642</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.741642943169965</v>
+        <v>-3.559728498118468</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.012940725297037</v>
+        <v>1.085706503317637</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4823051007621704</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.799337387336073</v>
+        <v>2.835066216333451</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.679344944393844</v>
+        <v>-3.497430499342346</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.104195478604307</v>
+        <v>1.176961256624906</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4823051007621704</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.865672941132894</v>
+        <v>2.901401770130272</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.477554746728686</v>
+        <v>-3.295640301677188</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9872035593844972</v>
+        <v>1.059969337405096</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6803232929313248</v>
+        <v>0.7398713412602882</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.786775858148514</v>
+        <v>2.822504687145892</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.312741743649839</v>
+        <v>-3.130827298598341</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.123418992938211</v>
+        <v>1.19618477095881</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8451362960101717</v>
+        <v>0.9046843443391351</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.955953892317997</v>
+        <v>2.991682721315375</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.410482288274813</v>
+        <v>-3.228567843223316</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.098950511204265</v>
+        <v>1.171716289224864</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8292470178771916</v>
+        <v>0.888795066206155</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.961048061554253</v>
+        <v>2.996776890551631</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.586820048397742</v>
+        <v>-3.404905603346245</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.026951387979765</v>
+        <v>1.099717166000364</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6529092577542621</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.853781386305167</v>
+        <v>2.889510215302545</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.510398001965815</v>
+        <v>-3.328483556914318</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.056011824592464</v>
+        <v>1.128777602613064</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6529092577542621</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.852273004345095</v>
+        <v>2.888001833342473</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.466024870327247</v>
+        <v>-3.284110425275749</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.073623944683328</v>
+        <v>1.146389722703927</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6972823893928307</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.878759750763673</v>
+        <v>2.914488579761051</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.343190649440079</v>
+        <v>-3.161276204388582</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.117151427176786</v>
+        <v>1.189917205197385</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6972823893928307</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.873153544902263</v>
+        <v>2.908882373899641</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.295534918879024</v>
+        <v>-3.113620473827527</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.142595476429012</v>
+        <v>1.215361254449612</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7449381199538864</v>
+        <v>0.8044861682828498</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.908128740266701</v>
+        <v>2.943857569264079</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.195016760380269</v>
+        <v>-3.013102315328772</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.187695113203239</v>
+        <v>1.260460891223838</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8454562784526409</v>
+        <v>0.9050043267816044</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.973332008740678</v>
+        <v>3.009060837738057</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.255683350782658</v>
+        <v>-3.073768905731161</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.150183149518156</v>
+        <v>1.222948927538755</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7637579617341073</v>
+        <v>0.8233060100630707</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.911067691185431</v>
+        <v>2.946796520182809</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.21084494917426</v>
+        <v>-3.028930504122763</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.172216212772144</v>
+        <v>1.244981990792743</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7683013946789767</v>
+        <v>0.8278494430079402</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.917891453562981</v>
+        <v>2.953620282560359</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.230343405416268</v>
+        <v>-3.048428960364771</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.168577769906418</v>
+        <v>1.241343547927017</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7202167533990724</v>
+        <v>0.7797648017280359</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.893201608426117</v>
+        <v>2.928930437423495</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.186140568330368</v>
+        <v>-3.004226123278871</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.192138507268615</v>
+        <v>1.264904285289215</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7644195904849729</v>
+        <v>0.8239676388139363</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.925602913205494</v>
+        <v>2.961331742202872</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.223119595993811</v>
+        <v>-3.041205150942314</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.175756896672486</v>
+        <v>1.248522674693085</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8013934922763034</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.94619725474954</v>
+        <v>2.981926083746918</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.064828178454539</v>
+        <v>-2.882913733403042</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.290321228871234</v>
+        <v>1.363087006891833</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8013934922763034</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.99744501993258</v>
+        <v>3.033173848929958</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.857186174820062</v>
+        <v>-2.675271729768566</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.371818734919278</v>
+        <v>1.444584512939877</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.009035495910779</v>
+        <v>1.068583544239743</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.120470926707518</v>
+        <v>3.156199755704896</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.806154082097534</v>
+        <v>-2.624239637046037</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.387179800246559</v>
+        <v>1.459945578267158</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.060067588633308</v>
+        <v>1.119615636962271</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.146038410579305</v>
+        <v>3.181767239576683</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.740929900970329</v>
+        <v>-2.559015455918832</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.430456876790146</v>
+        <v>1.503222654810745</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.125291769760513</v>
+        <v>1.184839818089477</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.202360323348334</v>
+        <v>3.238089152345712</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.703502880899195</v>
+        <v>-2.521588435847698</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.44138865711788</v>
+        <v>1.514154435138479</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.130543307789695</v>
+        <v>1.190091356118658</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.201472218465123</v>
+        <v>3.237201047462501</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.723614536933904</v>
+        <v>-2.541700091882407</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.434600787035237</v>
+        <v>1.507366565055836</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.141570652787114</v>
+        <v>1.201118701116078</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.209345417794815</v>
+        <v>3.245074246792193</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.669869722506699</v>
+        <v>-2.487955277455202</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.61665648382733</v>
+        <v>1.689422261847929</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.151633962227576</v>
+        <v>1.21118201055654</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.375941174480302</v>
+        <v>3.41167000347768</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.595087461481686</v>
+        <v>-2.413173016430189</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.766682297455152</v>
+        <v>1.839448075475751</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.226416223252589</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.540923440313128</v>
+        <v>3.576652269310506</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.569003377217878</v>
+        <v>-2.387088932166381</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.768823907174534</v>
+        <v>1.841589685195133</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.226416223252589</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.532631416326987</v>
+        <v>3.568360245324365</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.490872196368931</v>
+        <v>-2.308957751317434</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.798269575097893</v>
+        <v>1.871035353118492</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.300593034136273</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.575330698440977</v>
+        <v>3.611059527438355</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.481979734975648</v>
+        <v>-2.300065289924151</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.819380965381997</v>
+        <v>1.892146743402596</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.300593034136273</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.592885104167768</v>
+        <v>3.628613933165146</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.650455851945526</v>
+        <v>-2.468541406894029</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.74384556599863</v>
+        <v>1.816611344019229</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.272645198419693</v>
+        <v>1.332193246748656</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.567971450142403</v>
+        <v>3.603700279139781</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.952656323083943</v>
+        <v>-1.770741878032446</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.004235074731125</v>
+        <v>2.077000852751724</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.202297139049282</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.507032311708019</v>
+        <v>3.542761140705397</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.92993521940079</v>
+        <v>-1.748020774349293</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.003987538701291</v>
+        <v>2.07675331672189</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.202297139049282</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.497696334204924</v>
+        <v>3.533425163202302</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.928210176110747</v>
+        <v>-1.74629573105925</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.163583681868477</v>
+        <v>2.236349459889076</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.204022182339326</v>
+        <v>1.263570230668289</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.657637486030119</v>
+        <v>3.693366315027497</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.082991182889002</v>
+        <v>-1.901076737837505</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.138749101650822</v>
+        <v>2.211514879671421</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.17065450828485</v>
+        <v>1.230202556613813</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.674694704091079</v>
+        <v>3.710423533088457</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.075936492673828</v>
+        <v>-1.894022047622331</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.138246333726436</v>
+        <v>2.211012111747035</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.177709198500023</v>
+        <v>1.237257246828987</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.675602874209729</v>
+        <v>3.711331703207107</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.04898526834734</v>
+        <v>-1.867070823295843</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.159032977101773</v>
+        <v>2.231798755122372</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.192589544527743</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.694537235471102</v>
+        <v>3.73026606446848</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.184938276403656</v>
+        <v>-2.003023831352159</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.288754906024206</v>
+        <v>2.361520684044805</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.192589544527743</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.878640367616062</v>
+        <v>3.91436919661344</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.207346394208528</v>
+        <v>-2.025431949157031</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.271908353805251</v>
+        <v>2.34467413182585</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.192589544527743</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.870757062519055</v>
+        <v>3.906485891516433</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.355352161687928</v>
+        <v>-2.173437716636431</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.214760046363128</v>
+        <v>2.287525824383727</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.105862535664201</v>
+        <v>1.165410583993165</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.820774856750567</v>
+        <v>3.856503685747946</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.364793087576458</v>
+        <v>-2.182878642524961</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.267237393729563</v>
+        <v>2.340003171750162</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.228289653207593</v>
+        <v>1.287837701536556</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.950484844998449</v>
+        <v>3.986213673995827</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.417066694912099</v>
+        <v>-2.235152249860602</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.249219045340608</v>
+        <v>2.321984823361207</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.176016045871951</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.922011775142366</v>
+        <v>3.957740604139744</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.493396672513005</v>
+        <v>-2.311482227461508</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.21679886719402</v>
+        <v>2.28956464521462</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.176016045871951</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.920123588036141</v>
+        <v>3.955852417033519</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.605153625128306</v>
+        <v>-2.423239180076809</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.166916315750762</v>
+        <v>2.239682093771362</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.06425909325665</v>
+        <v>1.123807141585614</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.847889646069822</v>
+        <v>3.8836184750672</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.603312606070055</v>
+        <v>-2.421398161018558</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.166086733584216</v>
+        <v>2.238852511604814</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.065527319928119</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.847084592282856</v>
+        <v>3.882813421280234</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.735613898167608</v>
+        <v>-2.553699453116111</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.126239623611113</v>
+        <v>2.199005401631712</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.065527319928119</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.860157999148774</v>
+        <v>3.895886828146153</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.737175540982468</v>
+        <v>-2.555261095930971</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.125614966485168</v>
+        <v>2.198380744505767</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.065527319928119</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.860157999148774</v>
+        <v>3.895886828146153</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.765076328091941</v>
+        <v>-2.583161883040444</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.112978692768381</v>
+        <v>2.18574447078898</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.030930395785184</v>
+        <v>1.090478444114147</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.837923885790016</v>
+        <v>3.873652714787394</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.887602430794835</v>
+        <v>-2.705687985743338</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.060732695664423</v>
+        <v>2.133498473685021</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.90840429308229</v>
+        <v>0.9679523414112534</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.761172668145478</v>
+        <v>3.796901497142856</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.907663752071342</v>
+        <v>-2.725749307019845</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.119414126744323</v>
+        <v>2.192179904764923</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8883429718057829</v>
+        <v>0.9478910201347464</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.815841834970078</v>
+        <v>3.851570663967456</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.164384570066166</v>
+        <v>-2.982470125014669</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.157037518548241</v>
+        <v>2.22980329656884</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.891104809485636</v>
+        <v>3.926833638483013</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.318370987842306</v>
+        <v>-3.13645654279081</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.164423220583425</v>
+        <v>2.237188998604024</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.960085078631275</v>
+        <v>3.995813907628653</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.267849084014641</v>
+        <v>-3.085934638963144</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.170683184234612</v>
+        <v>2.243448962255211</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.946136280751396</v>
+        <v>3.981865109748775</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.520324238022365</v>
+        <v>-3.338409792970868</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.081563611686936</v>
+        <v>2.154329389707535</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.95800676980681</v>
+        <v>3.993735598804188</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.789797039944073</v>
+        <v>-3.607882594892576</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.974985025437197</v>
+        <v>2.047750803457796</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7799283976619681</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.959217304325754</v>
+        <v>3.994946133323132</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.947341111673514</v>
+        <v>-3.765426666622017</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.916089138972741</v>
+        <v>1.988854916993341</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7130265925216936</v>
+        <v>0.7725746408506571</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.923197963468911</v>
+        <v>3.958926792466289</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.07619166237556</v>
+        <v>-3.894277217324064</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.859626771428113</v>
+        <v>1.932392549448712</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6720331836709721</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.893679770894667</v>
+        <v>3.929408599892046</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.193159355014451</v>
+        <v>-4.011244909962955</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.9750437510716</v>
+        <v>2.047809529092199</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6720331836709721</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.055883827593711</v>
+        <v>4.09161265659109</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.277877297235404</v>
+        <v>-4.095962852183908</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.936003212147033</v>
+        <v>2.008768990167632</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5869171547429257</v>
+        <v>0.6464652030718891</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.999660848200698</v>
+        <v>4.035389677198076</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.359812115504288</v>
+        <v>-4.177897670452792</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.913458702407971</v>
+        <v>1.98622448042857</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5769824091558455</v>
+        <v>0.636530457484809</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.00392941841694</v>
+        <v>4.039658247414319</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.306073942104025</v>
+        <v>-4.124159497052529</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.943879610223978</v>
+        <v>2.016645388244577</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6307205825561076</v>
+        <v>0.6902686308850711</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.045097960913001</v>
+        <v>4.080826789910379</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.196067658626804</v>
+        <v>-4.014153213575308</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.980035010859042</v>
+        <v>2.052800788879641</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6539251544733828</v>
+        <v>0.7134732028023463</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.051173591307541</v>
+        <v>4.086902420304919</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.053008082885878</v>
+        <v>-3.871093637834382</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.041508851877387</v>
+        <v>2.114274629897985</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.6619385810633621</v>
+        <v>0.7214866293923256</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.060231657983503</v>
+        <v>4.095960486980881</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.751561357414041</v>
+        <v>-3.569646912362545</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.169348424948658</v>
+        <v>2.242114202969256</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9633853065351994</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.248360576149141</v>
+        <v>4.284089405146519</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.80651655385711</v>
+        <v>-3.624602108805614</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.148337524124141</v>
+        <v>2.221103302144739</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9633853065351994</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.249331753901852</v>
+        <v>4.28506058289923</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859304</v>
+        <v>3.821198342859305</v>
       </c>
       <c r="C2031" t="n">
         <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.755478177850589</v>
+        <v>-3.460588395928506</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.169595778906504</v>
+        <v>2.287551691675338</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.9633853065351994</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.250174658281607</v>
+        <v>4.285903487278985</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.776123010868705</v>
+        <v>3.777966059085855</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.607663610959577</v>
+        <v>3.604432262182533</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.755478177850589</v>
+        <v>-3.460588395928506</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.169595778906504</v>
+        <v>2.287551691675338</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.9633853065351994</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.600727407945945</v>
+        <v>3.5974960591689</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>101.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>112.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>103.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-642.2%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-46.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-65.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.6%</t>
+          <t>-458.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-257.3%</t>
+          <t>-215.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.5%</t>
+          <t>-85.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.0%</t>
+          <t>-132.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-121.7%</t>
+          <t>-138.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-116.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.3%</t>
+          <t>-34.1%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.36434170361416</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.791997431992835</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.562879052093717</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.614212383628741</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.693818283441618</v>
+        <v>2.107616792968217</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.526540953876159</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.558985110749975</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.820724160515763</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.607319631343068</v>
+        <v>2.021118140869667</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>3.398739946400204</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.560758037450235</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.140068235596265</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.481354928011126</v>
+        <v>1.895153437537726</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>3.400512873100463</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.547090924917639</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.571874028746052</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.294965498218616</v>
+        <v>1.708764007745216</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>3.304995262703108</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.53537569991973</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.806568022878604</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.189372675567685</v>
+        <v>1.603171185094285</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>3.297081798042751</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.533956291575695</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.142230670109057</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.05368820833147</v>
+        <v>1.46748671785807</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>3.254903798405373</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.540443851809937</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.218675000311928</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.029598036484562</v>
+        <v>1.443396546011162</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>3.309658664095812</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.539698366815768</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.583802382950675</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8828015984348951</v>
+        <v>1.296600107961495</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>3.131126708522236</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.538459910830527</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.992391160131353</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7181276315773832</v>
+        <v>1.131926141103982</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.884734986228588</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.533645343301988</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.106151572154218</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6678088992396978</v>
+        <v>1.081607408766297</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.879920418700049</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.531639393910865</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.522543446441215</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4992462001337761</v>
+        <v>0.9130447096603755</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.877914469308926</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.541898084579544</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.766814847168285</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4117963305116272</v>
+        <v>0.8255948400382267</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.888173159977605</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.537997649725239</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972065866405045</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3257954879626186</v>
+        <v>0.7395939974892176</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.8842727251233</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.53640256978024</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020268683647389</v>
+        <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3049192811206818</v>
+        <v>0.7187177906472813</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.882677645178301</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.540181545709448</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.316930025457586</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1900337203258111</v>
+        <v>0.6038322298524101</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.845210739667182</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.536155241175045</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.503649733766889</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1113195324676868</v>
+        <v>0.5251180419942862</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.841184435132779</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.536053139853461</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.88665112250952</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.04198312435094964</v>
+        <v>0.3718153851756494</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.841082333811195</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.538624655824891</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.891137567710909</v>
+        <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.04120618646007523</v>
+        <v>0.3725923230665242</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.840961982661792</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.543974959122941</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.250667890214912</v>
+        <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.179668012163626</v>
+        <v>0.2341304973629734</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.846312285959842</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.551890979080119</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.301016953669134</v>
+        <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1918916175881371</v>
+        <v>0.2219068919384619</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.824018867844487</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.554932729701888</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.39863623109053</v>
+        <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2278975779349266</v>
+        <v>0.1859009315916724</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.768489052013417</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.55782628602346</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.452707730598888</v>
+        <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2466326214166981</v>
+        <v>0.1671658881099014</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.738939708629974</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.563339483142102</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.656965905928752</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.322822694430001</v>
+        <v>0.09097581509659802</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.667869538980223</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.567822037626538</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.690618744437225</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3318012753489543</v>
+        <v>0.08199723417764471</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.612104072714437</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.58319373911996</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.617148912769776</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2870416411885537</v>
+        <v>0.1267568683380453</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.671557673208327</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.597748959867476</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.79227333015632</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3425361873956545</v>
+        <v>0.07126232213094497</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.581038243523917</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.59052979496588</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.026725424170809</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4435361899030461</v>
+        <v>-0.02973768037644708</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.573819078622321</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.583857604191904</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.131100155197256</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4919582730876009</v>
+        <v>-0.07815976356100185</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.504522049232478</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.58497339403046</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.183886310797583</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5119569454891755</v>
+        <v>-0.09815843596257601</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.448232547121596</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.587667122659575</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.309923104165872</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5596779342073765</v>
+        <v>-0.1458794246807771</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.466077249436556</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.591657458345976</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.252851332269941</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5328588897626032</v>
+        <v>-0.1190603802360037</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.470067585122957</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.590182231447234</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.394523173994061</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.591002853350993</v>
+        <v>-0.1772043438243935</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.468592358224215</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.605235641612107</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.344932329569227</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5561131054161872</v>
+        <v>-0.1423145958895877</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.513400275043987</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.592184507965424</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.19601399509737</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5095969052741274</v>
+        <v>-0.09579839574752791</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.519098895838408</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.601763581001632</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.970168842377959</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4096797711501541</v>
+        <v>0.004118738376444497</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.553833974226915</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.602902725557691</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.845590186040367</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3587091640590585</v>
+        <v>0.05508934546754007</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.554973118782974</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.605536499719799</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.898485474084653</v>
+        <v>-8.886247848949704</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3772335051146651</v>
+        <v>0.05068093582616973</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.726627134615708</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.569560218950374</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.611270203958435</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.826352298796772</v>
+        <v>-8.814114673661823</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3426465307608764</v>
+        <v>0.08526791017995849</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.726627134615708</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.575293923189011</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.60153294156457</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.754985906187125</v>
+        <v>-8.742748281052176</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3238372361108826</v>
+        <v>0.1040772048299523</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.65526074200606</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.608376496360934</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.591649460251662</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.6615268722019</v>
+        <v>-8.649289247066951</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2963371038297002</v>
+        <v>0.1315773371111346</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.65526074200606</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.598493015048026</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.589814899752289</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.394285071333503</v>
+        <v>-8.382047446198554</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.191274943981715</v>
+        <v>0.2366394969591199</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.65526074200606</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.596658454548653</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.589514584778828</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.296378032657012</v>
+        <v>-8.284140407522063</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1524124434845797</v>
+        <v>0.2755019974562551</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.587274992145504</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.637149589491526</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.590183090924322</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.272424491681054</v>
+        <v>-8.260186866546105</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1421625209487027</v>
+        <v>0.2857519199921321</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.563321451169546</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.652190220222594</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.576922774762569</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.008364553358259</v>
+        <v>-7.996126928223309</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.04979886178133652</v>
+        <v>0.3781155791594983</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.29926151284675</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.79736586705452</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.574135741102269</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.301284929853421</v>
+        <v>-7.289047304718471</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2302459539602979</v>
+        <v>0.6581603949011328</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.29926151284675</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.794578833394219</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.57447936499011</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.26110063148723</v>
+        <v>-7.248863006352281</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2466632971946154</v>
+        <v>0.6745777381354503</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.259077214480559</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.819033036301775</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.573846186210867</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.097700760547868</v>
+        <v>-7.085463135412918</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3113900667911174</v>
+        <v>0.7393045077319522</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.095677343541197</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.916439780086149</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.581770615048719</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.864219538318269</v>
+        <v>-6.85198191318332</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4127069845208089</v>
+        <v>0.8406214254616442</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8621961213115981</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>3.064452942261761</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.57887840473576</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.714553147310754</v>
+        <v>-6.702315522175804</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.469681330610856</v>
+        <v>0.8975957715516909</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7692926300690621</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>3.117302826694323</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.574245891482787</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.582277673679868</v>
+        <v>-6.570040048544918</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5179590068102375</v>
+        <v>0.9458734477510724</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6370171564381755</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>3.192035597619882</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.577060952170424</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.426539341120126</v>
+        <v>-6.414301715985176</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5830694005217709</v>
+        <v>1.010983841462606</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4812788238784339</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>3.288293657843364</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.589967293394082</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.177539542436545</v>
+        <v>-6.165301917301595</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6955756612188622</v>
+        <v>1.123490102159697</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4812788238784339</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>3.301199999067022</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.461991363794864</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.283129532209649</v>
+        <v>-6.2708919070747</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5253637357104015</v>
+        <v>0.9532781766512368</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.5868688136515383</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>3.109870075603941</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.51053570567195</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.301864434328246</v>
+        <v>-6.289626809193297</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5664141167400492</v>
+        <v>0.994328557680884</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.5924648233116696</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>3.155056811684949</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.390656782983783</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.153924392920647</v>
+        <v>-6.141686767785697</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.5057112106149213</v>
+        <v>0.9336256515557562</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.5721439074031121</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>3.047370438541916</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.381942796730304</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.100954870666659</v>
+        <v>-6.088717245531709</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5181850332630384</v>
+        <v>0.9460994742038737</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5191743851491232</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>3.070438165640831</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.374982184635211</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.057406463895968</v>
+        <v>-6.045168838761018</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5286437838762215</v>
+        <v>0.9565582248170568</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5191743851491232</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>3.063477553545737</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.389444539016354</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.024043257417199</v>
+        <v>-6.01180563228225</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5564514208488722</v>
+        <v>0.9843658617897071</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5191743851491232</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>3.077939907926881</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.383976659475549</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.915784120294678</v>
+        <v>-5.903546495159728</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5942871961570759</v>
+        <v>1.022201637097911</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5191743851491232</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>3.072472028386076</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.381474753486126</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.792492985477547</v>
+        <v>-5.780255360342597</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.641101744094505</v>
+        <v>1.06901618503534</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.3958832503319927</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>3.143944803286931</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.389175731723451</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.771343786574104</v>
+        <v>-5.759106161439154</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6572624018932078</v>
+        <v>1.085176842834043</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3747340514285493</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>3.164335300866322</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.384956440070502</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.527578344590659</v>
+        <v>-5.515340719455709</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7505492870336363</v>
+        <v>1.178463727974471</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3747340514285493</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>3.160116009213373</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.387080753990518</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.425815524313364</v>
+        <v>-5.413577899178414</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7933787290645702</v>
+        <v>1.221293170005405</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3615149830361206</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>3.170171764168846</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.37982282897422</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.17596513036429</v>
+        <v>-5.16372750522934</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8860609616279023</v>
+        <v>1.313975402568737</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3615149830361206</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>3.162913839152548</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.383421952494869</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.000073037896857</v>
+        <v>-4.987835412761907</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9600169221355239</v>
+        <v>1.387931363076359</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3615149830361206</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>3.166512962673197</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.396749458549423</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.828626574874393</v>
+        <v>-4.816388949739443</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.041923013399063</v>
+        <v>1.469837454339898</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.1900685200136575</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>3.282708346541229</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.39576993616572</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.754337009136054</v>
+        <v>-4.742099384001104</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.070659317310696</v>
+        <v>1.498573758251531</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1157789542753182</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>3.326302563600529</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.400464737220037</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.69070126690212</v>
+        <v>-4.67846364176717</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.100808415258587</v>
+        <v>1.528722856199422</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.05214321204138367</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>3.369178809995207</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.381658996003833</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.5792745075762</v>
+        <v>-4.56703688244125</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.12657337777275</v>
+        <v>1.554487818713585</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.05214321204138367</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>3.350373068779003</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.38340207262871</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.338844010771339</v>
+        <v>-4.326606385636389</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.224488653119572</v>
+        <v>1.652403094060407</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1882872847634766</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.496374443486796</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367683</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.38733138646353</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.266601442600145</v>
+        <v>-4.254363817465195</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.25731499422287</v>
+        <v>1.685229435163705</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1882872847634766</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.500303757321616</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.38800997038087</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.213603120318757</v>
+        <v>-4.201365495183807</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.279192907052765</v>
+        <v>1.7071073479936</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.2436235437654155</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.53418409664012</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.385008041600864</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.10479823483903</v>
+        <v>-4.09256060970408</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.319712932464649</v>
+        <v>1.747627373405484</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.2436235437654155</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.531182167860113</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.386587078611478</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.884777436802019</v>
+        <v>-3.872539811667069</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.409300288690068</v>
+        <v>1.837214729630903</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3848433888333957</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.617493111911515</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.402481261413301</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.751909747738741</v>
+        <v>-3.739672122603791</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.478341547117203</v>
+        <v>1.906255988058037</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3848433888333957</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.633387294713339</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.403627105853603</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.631736664374242</v>
+        <v>-3.619499039239292</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.527556624903304</v>
+        <v>1.955471065844139</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.5050164721978947</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.70663698917234</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.413715208415043</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.487064519274504</v>
+        <v>-3.474826894139555</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.595513585504639</v>
+        <v>2.023428026445474</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.6496886172976322</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.803528378793622</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.399752699816469</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.546939346632197</v>
+        <v>-3.534701721497247</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.557601145962988</v>
+        <v>1.985515586903823</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.58981378993994</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.753640973780433</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>3.415041869050677</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.427119115721359</v>
+        <v>-3.41488149058641</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.620818407561531</v>
+        <v>2.048732848502366</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.58981378993994</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.768930143014642</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>3.322686068373119</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.429588822183165</v>
+        <v>-3.417351197048216</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.52747472429925</v>
+        <v>1.955389165240085</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.5873440834781338</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.675092518459999</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>3.24194792985842</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.497959008507175</v>
+        <v>-3.485721383372225</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.419388511254948</v>
+        <v>1.847302952195783</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5966197825143488</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.59991979936703</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>3.232384638490311</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.626090800996107</v>
+        <v>-3.499509436219272</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.358572502891266</v>
+        <v>1.832224439688855</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5966197825143488</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.590356507998921</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.634074812643843</v>
+        <v>3.057094203530698</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.657083960324813</v>
+        <v>-3.530502595547977</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.170884804200171</v>
+        <v>1.64453674099776</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5966197825143488</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>3.415066073039308</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.638642044635631</v>
+        <v>3.061661435522486</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.481609700532343</v>
+        <v>-3.355028335755508</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.245641740108946</v>
+        <v>1.719293676906535</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5966197825143488</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>3.419633305031096</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.614384073396838</v>
+        <v>3.037403464283693</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.592545953173592</v>
+        <v>-3.465964588396757</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.177009267813654</v>
+        <v>1.650661204611243</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5966197825143488</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>3.395375333792303</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.542922386798288</v>
+        <v>2.965941777685143</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.55888240770131</v>
+        <v>-3.432301042924475</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.119012999404017</v>
+        <v>1.592664936201606</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6302833279866307</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>3.344111774477121</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.55309477323042</v>
+        <v>2.976114164117275</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.499029788497587</v>
+        <v>-3.372448423720752</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.153126433517638</v>
+        <v>1.626778370315227</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6302833279866307</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>3.354284160909254</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.54804104380428</v>
+        <v>2.971060434691136</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.41278632547121</v>
+        <v>-3.286204960694374</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.182570089302049</v>
+        <v>1.656222026099639</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6302833279866307</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>3.349230431483114</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.539816819248806</v>
+        <v>2.962836210135661</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.458093144870189</v>
+        <v>-3.331511780093354</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.156223136986983</v>
+        <v>1.629875073784572</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5894731649773999</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>3.316520109122101</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.540368692281907</v>
+        <v>2.963388083168763</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.487126249572491</v>
+        <v>-3.360544884795656</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.145161768139164</v>
+        <v>1.618813704936753</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5894731649773999</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>3.317071982155203</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.469641384173273</v>
+        <v>2.892660775060128</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.394315768121632</v>
+        <v>-3.267734403344797</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.111558652610873</v>
+        <v>1.585210589408462</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.6822836464282592</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>3.302030962917084</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.471514860097874</v>
+        <v>2.894534250984729</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.438705237451059</v>
+        <v>-3.312123872674224</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.095676340803703</v>
+        <v>1.569328277601292</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.6378941770988316</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>3.277270757244028</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.466590568609597</v>
+        <v>2.889609959496452</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.326034019214809</v>
+        <v>-3.199452654437974</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.135820536609926</v>
+        <v>1.609472473407515</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.7505653953350817</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>3.339949196697502</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.472081864440264</v>
+        <v>2.895101255327119</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.213657018032137</v>
+        <v>-3.087075653255301</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.186262632913663</v>
+        <v>1.659914569711252</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.7505653953350817</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>3.345440492528168</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.483579066208803</v>
+        <v>2.906598457095658</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.24143741593349</v>
+        <v>-3.114856051156655</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.18664767552166</v>
+        <v>1.660299612319249</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.7227849974337286</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>3.340269455555896</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.321934786209456</v>
+        <v>2.744954177096312</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.359818088663628</v>
+        <v>-3.233236723886793</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9776511264302581</v>
+        <v>1.451303063227847</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.6555671452827524</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.706294955026883</v>
+        <v>3.138294464265964</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.442084446928662</v>
+        <v>2.865103837815517</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.468432167106959</v>
+        <v>-3.341850802330124</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.054355155772131</v>
+        <v>1.52800709256972</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.6555671452827524</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.826444615746089</v>
+        <v>3.258444124985169</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.456597473030985</v>
+        <v>2.87961686391784</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.433023128858816</v>
+        <v>-3.306441764081981</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.083031797173712</v>
+        <v>1.556683733971301</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.6555671452827524</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.840957641848412</v>
+        <v>3.272957151087492</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.454016914373354</v>
+        <v>2.877036305260209</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.394639466300665</v>
+        <v>-3.26805810152383</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.095804703539341</v>
+        <v>1.56945664033693</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.678983943920529</v>
+        <v>0.6939508078409036</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.861407280725671</v>
+        <v>3.293406789964751</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.450745943218656</v>
+        <v>2.873765334105511</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.217523136265499</v>
+        <v>-3.090941771488664</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.163380264398709</v>
+        <v>1.637032201196298</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.678983943920529</v>
+        <v>0.6939508078409036</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.858136309570973</v>
+        <v>3.290135818810053</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.451429334980569</v>
+        <v>2.874448725867424</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.262615381099045</v>
+        <v>-3.13603401632221</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.146026758227204</v>
+        <v>1.619678695024793</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6170879007511392</v>
+        <v>0.6320547646715138</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.821682075431252</v>
+        <v>3.253681584670332</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.445216310286983</v>
+        <v>2.868235701173838</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.083239959860277</v>
+        <v>-2.956658595083442</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.211563902029125</v>
+        <v>1.685215838826714</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7738646589218579</v>
+        <v>0.7888315228422325</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.909535105640098</v>
+        <v>3.341534614879178</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.426023765618573</v>
+        <v>2.849043156505428</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.128254173380884</v>
+        <v>-3.001672808604048</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.174365671952472</v>
+        <v>1.648017608750062</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7435157636072532</v>
+        <v>0.7584826275276279</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.872133223782925</v>
+        <v>3.304132733022005</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.431715327957519</v>
+        <v>2.854734718844374</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.395258683653319</v>
+        <v>-3.268677318876484</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.073255430182444</v>
+        <v>1.546907366980033</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5491527255643047</v>
+        <v>0.5641195894846793</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.761206963296102</v>
+        <v>3.193206472535182</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.43091924985402</v>
+        <v>2.853938640740875</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.496456465090492</v>
+        <v>-3.369875100313656</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031980239504076</v>
+        <v>1.505632176301666</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4957107759393602</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.719365597065412</v>
+        <v>3.151365106304492</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.428519211408337</v>
+        <v>2.851538602295192</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.489945498476179</v>
+        <v>-3.363364133699344</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.032184587704118</v>
+        <v>1.505836524501707</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.4957107759393602</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.716965558619728</v>
+        <v>3.148965067858808</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.425043930616582</v>
+        <v>2.848063321503437</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.470907370768882</v>
+        <v>-3.344326005992047</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.036324557995282</v>
+        <v>1.509976494792871</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.422560300687791</v>
+        <v>0.4375271646081657</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.678580111029257</v>
+        <v>3.110579620268337</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.602625799555262</v>
+        <v>3.025645190442118</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.5020340019195</v>
+        <v>-3.375452637142665</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201455774473715</v>
+        <v>1.675107711271304</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.422560300687791</v>
+        <v>0.4375271646081657</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.856161979967937</v>
+        <v>3.288161489207017</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.603459128541396</v>
+        <v>3.026478519428251</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.515900763253417</v>
+        <v>-3.389319398476582</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.196742398926282</v>
+        <v>1.670394335723871</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.3996692478743427</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.834280558913777</v>
+        <v>3.266280068152857</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.609467658938322</v>
+        <v>3.032487049825177</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.594800193724532</v>
+        <v>-3.344515226936652</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.171191157134762</v>
+        <v>1.694324534736769</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.3996692478743427</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.840289089310703</v>
+        <v>3.272288598549783</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.507417880215521</v>
+        <v>2.930437271102377</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.44705722348953</v>
+        <v>-3.19677225670165</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.128238566505962</v>
+        <v>1.651371944107969</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.5674766051092259</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.838923724928832</v>
+        <v>3.270923234167912</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.510211501747002</v>
+        <v>2.933230892633858</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.549071906020751</v>
+        <v>-3.298786939232871</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.090226315024955</v>
+        <v>1.613359692626962</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.5674766051092259</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.841717346460313</v>
+        <v>3.273716855699393</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.51087385013866</v>
+        <v>2.933893241025516</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.542919199967967</v>
+        <v>-3.292634233180086</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.093349745837727</v>
+        <v>1.616483123439734</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5586624472416355</v>
+        <v>0.5736293111620102</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.846071318483642</v>
+        <v>3.278070827722722</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.509954326878771</v>
+        <v>2.932973717765626</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.559728498118468</v>
+        <v>-3.309443531330588</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.085706503317637</v>
+        <v>1.608839880919644</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.5568200130115086</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.835066216333451</v>
+        <v>3.267065725572531</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.576289880675592</v>
+        <v>2.999309271562447</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.497430499342346</v>
+        <v>-3.247145532554466</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.176961256624906</v>
+        <v>1.700094634226913</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.5568200130115086</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.901401770130272</v>
+        <v>3.333401279369352</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.378581882389719</v>
+        <v>2.801601273276574</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.295640301677188</v>
+        <v>-3.281517451856905</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.059969337405096</v>
+        <v>1.488637868220065</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7398713412602882</v>
+        <v>0.5760371890237018</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.822504687145892</v>
+        <v>3.147223586690795</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.448872114711894</v>
+        <v>2.871891505598749</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.130827298598341</v>
+        <v>-3.116704448778058</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.19618477095881</v>
+        <v>1.624853301773779</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9046843443391351</v>
+        <v>0.7408501921025488</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.991682721315375</v>
+        <v>3.316401620860279</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.463499850827938</v>
+        <v>2.886519241714793</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.228567843223316</v>
+        <v>-3.214444993403032</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.171716289224864</v>
+        <v>1.600384820039833</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.888795066206155</v>
+        <v>0.7249609139695685</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.996776890551631</v>
+        <v>3.321495790096535</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.462035831652609</v>
+        <v>2.885055222539465</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.404905603346245</v>
+        <v>-3.390782753525961</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.099717166000364</v>
+        <v>1.528385696815333</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.5486231538466391</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.889510215302545</v>
+        <v>3.214229114847448</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.460527449692538</v>
+        <v>2.883546840579393</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.328483556914318</v>
+        <v>-3.314360707094035</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.128777602613064</v>
+        <v>1.557446133428032</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.5486231538466391</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.888001833342473</v>
+        <v>3.212720732887377</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.460390317127974</v>
+        <v>2.883409708014829</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.284110425275749</v>
+        <v>-3.269987575455466</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.146389722703927</v>
+        <v>1.575058253518896</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.5929962854852077</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.914488579761051</v>
+        <v>3.239207479305954</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.454784111266564</v>
+        <v>2.87780350215342</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.161276204388582</v>
+        <v>-3.147153354568299</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.189917205197385</v>
+        <v>1.618585736012353</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.5929962854852077</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.908882373899641</v>
+        <v>3.233601273444545</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.461165868294369</v>
+        <v>2.884185259181224</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.113620473827527</v>
+        <v>-3.099497624007243</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.215361254449612</v>
+        <v>1.64402978526458</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8044861682828498</v>
+        <v>0.6406520160462633</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.943857569264079</v>
+        <v>3.268576468808983</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.466058241669094</v>
+        <v>2.889077632555949</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.013102315328772</v>
+        <v>-2.998979465508488</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.260460891223838</v>
+        <v>1.689129422038807</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9050043267816044</v>
+        <v>0.7411701745450179</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.009060837738057</v>
+        <v>3.33377973728296</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.452812914144966</v>
+        <v>2.875832305031822</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.073768905731161</v>
+        <v>-3.059646055910877</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.222948927538755</v>
+        <v>1.651617458353723</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8233060100630707</v>
+        <v>0.6594718578264842</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.946796520182809</v>
+        <v>3.271515419727712</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.456910616755595</v>
+        <v>2.87993000764245</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.028930504122763</v>
+        <v>-3.014807654302479</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.244981990792743</v>
+        <v>1.673650521607711</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8278494430079402</v>
+        <v>0.6640152907713537</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.953620282560359</v>
+        <v>3.278339182105263</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.461071556386673</v>
+        <v>2.884090947273528</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.048428960364771</v>
+        <v>-3.034306110544487</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.241343547927017</v>
+        <v>1.670012078741986</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7797648017280359</v>
+        <v>0.6159306494914494</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.928930437423495</v>
+        <v>3.253649336968398</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.46695115891451</v>
+        <v>2.889970549801365</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.004226123278871</v>
+        <v>-2.990103273458587</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.264904285289215</v>
+        <v>1.693572816104183</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8239676388139363</v>
+        <v>0.6601334865773498</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.961331742202872</v>
+        <v>3.286050641747775</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.465361159383757</v>
+        <v>2.888380550270613</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.041205150942314</v>
+        <v>-3.02708230112203</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.248522674693085</v>
+        <v>1.677191205508054</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.6971073883686804</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.981926083746918</v>
+        <v>3.306644983291821</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.516608924566797</v>
+        <v>2.939628315453652</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.882913733403042</v>
+        <v>-2.868790883582758</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.363087006891833</v>
+        <v>1.791755537706802</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.6971073883686804</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.033173848929958</v>
+        <v>3.357892748474861</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.51504962916105</v>
+        <v>2.938069020047906</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.675271729768566</v>
+        <v>-2.661148879948282</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.444584512939877</v>
+        <v>1.873253043754846</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.068583544239743</v>
+        <v>0.9047493920031565</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.156199755704896</v>
+        <v>3.4809186552498</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.50999785739932</v>
+        <v>2.933017248286176</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.624239637046037</v>
+        <v>-2.610116787225754</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.459945578267158</v>
+        <v>1.888614109082127</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.119615636962271</v>
+        <v>0.9557814847256845</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.181767239576683</v>
+        <v>3.506486139121586</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.527185261492025</v>
+        <v>2.950204652378881</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.559015455918832</v>
+        <v>-2.544892606098548</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.503222654810745</v>
+        <v>1.931891185625714</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.184839818089477</v>
+        <v>1.02100566585289</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.238089152345712</v>
+        <v>3.562808051890615</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.523146233791306</v>
+        <v>2.946165624678161</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.521588435847698</v>
+        <v>-2.507465586027414</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.514154435138479</v>
+        <v>1.942822965953448</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.190091356118658</v>
+        <v>1.026257203882072</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.237201047462501</v>
+        <v>3.561919947007404</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.524403026122546</v>
+        <v>2.947422417009401</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.541700091882407</v>
+        <v>-2.527577242062123</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.507366565055836</v>
+        <v>1.936035095870805</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.201118701116078</v>
+        <v>1.037284548879491</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.245074246792193</v>
+        <v>3.569793146337096</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.684960797143757</v>
+        <v>3.107980188030612</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.487955277455202</v>
+        <v>-2.473832427634918</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.689422261847929</v>
+        <v>2.118090792662898</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.21118201055654</v>
+        <v>1.047347858319953</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.41167000347768</v>
+        <v>3.736388903022584</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.805073706361574</v>
+        <v>3.228093097248429</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.413173016430189</v>
+        <v>-2.399050166609905</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.839448075475751</v>
+        <v>2.26811660629072</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.285964271581552</v>
+        <v>1.122130119344966</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.576652269310506</v>
+        <v>3.901371168855409</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.796781682375433</v>
+        <v>3.219801073262288</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.387088932166381</v>
+        <v>-2.372966082346097</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.841589685195133</v>
+        <v>2.270258216010102</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.285964271581552</v>
+        <v>1.122130119344966</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.568360245324365</v>
+        <v>3.893079144869268</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.794974877959212</v>
+        <v>3.217994268846068</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.308957751317434</v>
+        <v>-2.294834901497151</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.871035353118492</v>
+        <v>2.29970388393346</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360141082465237</v>
+        <v>1.19630693022865</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.611059527438355</v>
+        <v>3.935778426983259</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.812529283686004</v>
+        <v>3.235548674572859</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.300065289924151</v>
+        <v>-2.285942440103867</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.892146743402596</v>
+        <v>2.320815274217565</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360141082465237</v>
+        <v>1.19630693022865</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.628613933165146</v>
+        <v>3.95333283271005</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.804384331090588</v>
+        <v>3.227403721977443</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.468541406894029</v>
+        <v>-2.454418557073745</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.816611344019229</v>
+        <v>2.245279874834198</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332193246748656</v>
+        <v>1.16835909451207</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.603700279139781</v>
+        <v>3.928419178684685</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.785654028278449</v>
+        <v>3.208673419165305</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.770741878032446</v>
+        <v>-1.756619028212162</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.077000852751724</v>
+        <v>2.505669383566693</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.261845187378245</v>
+        <v>1.098011035141659</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.542761140705397</v>
+        <v>3.8674800402503</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.776318050775354</v>
+        <v>3.199337441662209</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.748020774349293</v>
+        <v>-1.73389792452901</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.07675331672189</v>
+        <v>2.505421847536858</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.261845187378245</v>
+        <v>1.098011035141659</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533425163202302</v>
+        <v>3.858144062747205</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.935224176626523</v>
+        <v>3.358243567513378</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.74629573105925</v>
+        <v>-1.732172881238966</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.236349459889076</v>
+        <v>2.665017990704045</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.263570230668289</v>
+        <v>1.099736078431703</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.693366315027497</v>
+        <v>4.0180852145724</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.97230199912017</v>
+        <v>3.395321390007025</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.901076737837505</v>
+        <v>-1.886953888017221</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.211514879671421</v>
+        <v>2.640183410486389</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.230202556613813</v>
+        <v>1.066368404377227</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.710423533088457</v>
+        <v>4.035142432633361</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.968977355109715</v>
+        <v>3.39199674599657</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.894022047622331</v>
+        <v>-1.879899197802047</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.211012111747035</v>
+        <v>2.639680642562004</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.237257246828987</v>
+        <v>1.0734230945924</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.711331703207107</v>
+        <v>4.03605060275201</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.978983508754456</v>
+        <v>3.402002899641312</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.867070823295843</v>
+        <v>-1.852947973475559</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.231798755122372</v>
+        <v>2.660467285937341</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.252137592856706</v>
+        <v>1.08830344062012</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.73026606446848</v>
+        <v>4.054984964013384</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.163086640899416</v>
+        <v>3.586106031786271</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.003023831352159</v>
+        <v>-1.988900981531875</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.361520684044805</v>
+        <v>2.790189214859774</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.252137592856706</v>
+        <v>1.08830344062012</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.91436919661344</v>
+        <v>4.239088096158343</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.155203335802409</v>
+        <v>3.578222726689265</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.025431949157031</v>
+        <v>-2.011309099336748</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.34467413182585</v>
+        <v>2.773342662640818</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.252137592856706</v>
+        <v>1.08830344062012</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.906485891516433</v>
+        <v>4.231204791061336</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.157257335352047</v>
+        <v>3.580276726238902</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.173437716636431</v>
+        <v>-2.159314866816147</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.287525824383727</v>
+        <v>2.716194355198696</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165410583993165</v>
+        <v>1.001576431756578</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.856503685747946</v>
+        <v>4.181222585292849</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.213511053073894</v>
+        <v>3.636530443960749</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.182878642524961</v>
+        <v>-2.168755792704677</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.340003171750162</v>
+        <v>2.768671702565131</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287837701536556</v>
+        <v>1.12400354929997</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.986213673995827</v>
+        <v>4.310932573540731</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.216402147619195</v>
+        <v>3.63942153850605</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.235152249860602</v>
+        <v>-2.221029400040318</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.321984823361207</v>
+        <v>2.750653354176175</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.235564094200915</v>
+        <v>1.071729941964328</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.957740604139744</v>
+        <v>4.282459503684647</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.21451396051297</v>
+        <v>3.637533351399825</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.311482227461508</v>
+        <v>-2.297359377641224</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.28956464521462</v>
+        <v>2.718233176029588</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.235564094200915</v>
+        <v>1.071729941964328</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.955852417033519</v>
+        <v>4.280571316578422</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.209334190115832</v>
+        <v>3.632353581002687</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.423239180076809</v>
+        <v>-2.409116330256525</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.239682093771362</v>
+        <v>2.66835062458633</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.123807141585614</v>
+        <v>0.9599729893490272</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.8836184750672</v>
+        <v>4.208337374612104</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.207768200325984</v>
+        <v>3.63078759121284</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.421398161018558</v>
+        <v>-2.407275311198274</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.238852511604814</v>
+        <v>2.667521042419783</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.125075368257082</v>
+        <v>0.9612412160204956</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.882813421280234</v>
+        <v>4.207532320825138</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.220841607191903</v>
+        <v>3.643860998078758</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.553699453116111</v>
+        <v>-2.539576603295827</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.199005401631712</v>
+        <v>2.62767393244668</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.125075368257082</v>
+        <v>0.9612412160204956</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.895886828146153</v>
+        <v>4.220605727691056</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.220841607191903</v>
+        <v>3.643860998078758</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.555261095930971</v>
+        <v>-2.541138246110688</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.198380744505767</v>
+        <v>2.627049275320736</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.125075368257082</v>
+        <v>0.9612412160204956</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.895886828146153</v>
+        <v>4.220605727691056</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.219365648318905</v>
+        <v>3.64238503920576</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.583161883040444</v>
+        <v>-2.56903903322016</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.18574447078898</v>
+        <v>2.614413001603949</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.090478444114147</v>
+        <v>0.9266442918775608</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.873652714787394</v>
+        <v>4.198371614332297</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.216130092296104</v>
+        <v>3.639149483182959</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.705687985743338</v>
+        <v>-2.691565135923054</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.133498473685021</v>
+        <v>2.56216700449999</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9679523414112534</v>
+        <v>0.8041181891746669</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.796901497142856</v>
+        <v>4.12162039668776</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.282836051886608</v>
+        <v>3.705855442773463</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.725749307019845</v>
+        <v>-2.711626457199561</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.192179904764923</v>
+        <v>2.620848435579891</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9478910201347464</v>
+        <v>0.7840568678981599</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.851570663967456</v>
+        <v>4.176289563512359</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.423147770888455</v>
+        <v>3.84616716177531</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.982470125014669</v>
+        <v>-2.968347275194385</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.22980329656884</v>
+        <v>2.658471827383809</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.675642293754345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.926833638483013</v>
+        <v>4.251552538027918</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.492128040034094</v>
+        <v>3.91514743092095</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.13645654279081</v>
+        <v>-3.122333692970526</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.237188998604024</v>
+        <v>2.665857529418992</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.675642293754345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.995813907628653</v>
+        <v>4.320532807173557</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.478179242154215</v>
+        <v>3.901198633041071</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.085934638963144</v>
+        <v>-3.07181178914286</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.243448962255211</v>
+        <v>2.672117493070179</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.675642293754345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.981865109748775</v>
+        <v>4.306584009293678</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.490049731209629</v>
+        <v>3.913069122096485</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.338409792970868</v>
+        <v>-3.324286943150584</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.154329389707535</v>
+        <v>2.582997920522504</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.675642293754345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.993735598804188</v>
+        <v>4.318454498349092</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.491260265728573</v>
+        <v>3.914279656615428</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.607882594892576</v>
+        <v>-3.593759745072292</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.047750803457796</v>
+        <v>2.476419334272764</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.675642293754345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.994946133323132</v>
+        <v>4.319665032868036</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.495382007955894</v>
+        <v>3.91840139884275</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.765426666622017</v>
+        <v>-3.751303816801733</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.988854916993341</v>
+        <v>2.41752344780831</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7725746408506571</v>
+        <v>0.6087404886140706</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.958926792466289</v>
+        <v>4.283645692011193</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.490459860692084</v>
+        <v>3.91347925157894</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.894277217324064</v>
+        <v>-3.88015436750378</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.932392549448712</v>
+        <v>2.36106108026368</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.567747079763349</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.929408599892046</v>
+        <v>4.254127499436949</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.652663917391128</v>
+        <v>4.075683308277984</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.011244909962955</v>
+        <v>-3.997122060142671</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.047809529092199</v>
+        <v>2.476478059907168</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.567747079763349</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.09161265659109</v>
+        <v>4.416331556135994</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.647510555354942</v>
+        <v>4.070529946241798</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.095962852183908</v>
+        <v>-4.081840002363625</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.008768990167632</v>
+        <v>2.437437520982601</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6464652030718891</v>
+        <v>0.4826310508353027</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.035389677198076</v>
+        <v>4.36010857674298</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.657739972923433</v>
+        <v>4.08075936381029</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.177897670452792</v>
+        <v>-4.163774820632508</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.98622448042857</v>
+        <v>2.41489301124354</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.636530457484809</v>
+        <v>0.4726963052482225</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.039658247414319</v>
+        <v>4.364377146959224</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.666665611379336</v>
+        <v>4.089685002266192</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.124159497052529</v>
+        <v>-4.110036647232246</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.016645388244577</v>
+        <v>2.445313919059546</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6902686308850711</v>
+        <v>0.5264344786484846</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.080826789910379</v>
+        <v>4.405545689455283</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.658818498623511</v>
+        <v>4.081837889510368</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.014153213575308</v>
+        <v>-4.000030363755024</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.052800788879641</v>
+        <v>2.481469319694611</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7134732028023463</v>
+        <v>0.5496390505657598</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.086902420304919</v>
+        <v>4.411621319849824</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.663068509345485</v>
+        <v>4.086087900232342</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.871093637834382</v>
+        <v>-3.856970788014098</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.114274629897985</v>
+        <v>2.542943160712955</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7214866293923256</v>
+        <v>0.5576524771557391</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.095960486980881</v>
+        <v>4.420679386525785</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.670329392228021</v>
+        <v>4.093348783114878</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.569646912362545</v>
+        <v>-3.555524062542261</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.242114202969256</v>
+        <v>2.670782733784227</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.022933354864163</v>
+        <v>0.8590992026275763</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.284089405146519</v>
+        <v>4.608808304691425</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.671300569980732</v>
+        <v>4.094319960867589</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.624602108805614</v>
+        <v>-3.61047925898533</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.221103302144739</v>
+        <v>2.64977183295971</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.022933354864163</v>
+        <v>0.8590992026275763</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.28506058289923</v>
+        <v>4.609779482444135</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859305</v>
+        <v>3.821198342859302</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.672143474360487</v>
+        <v>4.095162865247344</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.460588395928506</v>
+        <v>-2.965143380509428</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.287551691675338</v>
+        <v>2.908749088729826</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.022933354864163</v>
+        <v>0.8590992026275763</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.285903487278985</v>
+        <v>4.61062238682389</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.777966059085855</v>
+        <v>3.858096227715832</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.604432262182533</v>
+        <v>4.126098138708092</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.460588395928506</v>
+        <v>-2.965143380509428</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.287551691675338</v>
+        <v>2.908749088729826</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.022933354864163</v>
+        <v>0.8590992026275763</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.5974960591689</v>
+        <v>4.11916193569446</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>101.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.8%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.0%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.1%</t>
+          <t>-68.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>456.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-458.1%</t>
+          <t>-537.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-215.9%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-85.3%</t>
+          <t>-159.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.6%</t>
+          <t>-131.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-138.1%</t>
+          <t>-127.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-116.3%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-78.9%</t>
         </is>
       </c>
     </row>
@@ -44236,19 +44236,19 @@
         <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.562879052093717</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
         <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.107616792968217</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.526540953876159</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44259,19 +44259,19 @@
         <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.558985110749975</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
         <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.021118140869667</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.398739946400204</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.560758037450235</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
         <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.895153437537726</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.400512873100463</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.547090924917639</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
         <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.708764007745216</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.304995262703108</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.53537569991973</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
         <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.603171185094285</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.297081798042751</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.533956291575695</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
         <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.46748671785807</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.254903798405373</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.540443851809937</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
         <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.443396546011162</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.309658664095812</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.539698366815768</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
         <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.296600107961495</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.131126708522236</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.538459910830527</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.131926141103982</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.884734986228588</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.533645343301988</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
         <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.081607408766297</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.879920418700049</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.531639393910865</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
         <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9130447096603755</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.877914469308926</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.541898084579544</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
         <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8255948400382267</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.888173159977605</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.537997649725239</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
         <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7395939974892176</v>
+        <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.8842727251233</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.53640256978024</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
         <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.7187177906472813</v>
+        <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.882677645178301</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.540181545709448</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
         <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6038322298524101</v>
+        <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.845210739667182</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.536155241175045</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
         <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5251180419942862</v>
+        <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.841184435132779</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.536053139853461</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
         <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3718153851756494</v>
+        <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.841082333811195</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.538624655824891</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
         <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.3725923230665242</v>
+        <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.840961982661792</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.543974959122941</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
         <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.2341304973629734</v>
+        <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.846312285959842</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.551890979080119</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
         <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.2219068919384619</v>
+        <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.824018867844487</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.554932729701888</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
         <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.1859009315916724</v>
+        <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.768489052013417</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.55782628602346</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
         <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.1671658881099014</v>
+        <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.738939708629974</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.563339483142102</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
         <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.09097581509659802</v>
+        <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.667869538980223</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.567822037626538</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
         <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.08199723417764471</v>
+        <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.612104072714437</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.58319373911996</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
         <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.1267568683380453</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.671557673208327</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.597748959867476</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
         <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.07126232213094497</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.581038243523917</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.59052979496588</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
         <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.02973768037644708</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.573819078622321</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.583857604191904</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
         <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.07815976356100185</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.504522049232478</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.58497339403046</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
         <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.09815843596257601</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.448232547121596</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.587667122659575</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
         <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.1458794246807771</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.466077249436556</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.591657458345976</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
         <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.1190603802360037</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.470067585122957</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.590182231447234</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
         <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.1772043438243935</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.468592358224215</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.605235641612107</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
         <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1423145958895877</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.513400275043987</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.592184507965424</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
         <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.09579839574752791</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.519098895838408</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.601763581001632</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
         <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.004118738376444497</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.553833974226915</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.602902725557691</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
         <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.05508934546754007</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.554973118782974</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.605536499719799</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.886247848949704</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.05068093582616973</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.726627134615708</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.569560218950374</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.611270203958435</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.814114673661823</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.08526791017995849</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.726627134615708</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.575293923189011</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.60153294156457</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.742748281052176</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.1040772048299523</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.65526074200606</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.608376496360934</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.591649460251662</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.649289247066951</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1315773371111346</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.65526074200606</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.598493015048026</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.589814899752289</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.382047446198554</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2366394969591199</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.65526074200606</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.596658454548653</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.589514584778828</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.284140407522063</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2755019974562551</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.587274992145504</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.637149589491526</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.590183090924322</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.260186866546105</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2857519199921321</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.563321451169546</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.652190220222594</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.576922774762569</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.996126928223309</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3781155791594983</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.29926151284675</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.79736586705452</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.574135741102269</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.289047304718471</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.6581603949011328</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.29926151284675</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.794578833394219</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.57447936499011</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.248863006352281</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.6745777381354503</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.259077214480559</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.819033036301775</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.573846186210867</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.085463135412918</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.7393045077319522</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.095677343541197</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.916439780086149</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.581770615048719</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.85198191318332</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.8406214254616442</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8621961213115981</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.064452942261761</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.57887840473576</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.702315522175804</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.8975957715516909</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7692926300690621</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.117302826694323</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.574245891482787</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.570040048544918</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.9458734477510724</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6370171564381755</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.192035597619882</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.577060952170424</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.414301715985176</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.010983841462606</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4812788238784339</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.288293657843364</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.589967293394082</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.165301917301595</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.123490102159697</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4812788238784339</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.301199999067022</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.461991363794864</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.2708919070747</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.9532781766512368</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5868688136515383</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.109870075603941</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.51053570567195</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.289626809193297</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.994328557680884</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.5924648233116696</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.155056811684949</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.390656782983783</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.141686767785697</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9336256515557562</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5721439074031121</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.047370438541916</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.381942796730304</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.088717245531709</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.9460994742038737</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5191743851491232</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.070438165640831</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.374982184635211</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.045168838761018</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.9565582248170568</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5191743851491232</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.063477553545737</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.389444539016354</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.01180563228225</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.9843658617897071</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5191743851491232</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.077939907926881</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.383976659475549</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.903546495159728</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.022201637097911</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5191743851491232</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.072472028386076</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.381474753486126</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.780255360342597</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.06901618503534</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3958832503319927</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.143944803286931</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.389175731723451</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.759106161439154</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.085176842834043</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3747340514285493</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.164335300866322</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.384956440070502</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.515340719455709</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.178463727974471</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3747340514285493</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.160116009213373</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.387080753990518</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.413577899178414</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.221293170005405</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3615149830361206</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.170171764168846</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.37982282897422</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.16372750522934</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.313975402568737</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3615149830361206</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.162913839152548</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.383421952494869</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.987835412761907</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.387931363076359</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3615149830361206</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.166512962673197</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.396749458549423</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.816388949739443</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.469837454339898</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.1900685200136575</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.282708346541229</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.39576993616572</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.742099384001104</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.498573758251531</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1157789542753182</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.326302563600529</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.400464737220037</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.67846364176717</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.528722856199422</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.05214321204138367</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.369178809995207</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.381658996003833</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.56703688244125</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.554487818713585</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.05214321204138367</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.350373068779003</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.38340207262871</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.326606385636389</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.652403094060407</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1882872847634766</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.496374443486796</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.38733138646353</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.254363817465195</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.685229435163705</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1882872847634766</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.500303757321616</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.38800997038087</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.201365495183807</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.7071073479936</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2436235437654155</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.53418409664012</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.385008041600864</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.09256060970408</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.747627373405484</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2436235437654155</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.531182167860113</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.386587078611478</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.872539811667069</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.837214729630903</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3848433888333957</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.617493111911515</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.402481261413301</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.739672122603791</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.906255988058037</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3848433888333957</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.633387294713339</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.403627105853603</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.619499039239292</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.955471065844139</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5050164721978947</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.70663698917234</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.413715208415043</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.474826894139555</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>2.023428026445474</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6496886172976322</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.803528378793622</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.399752699816469</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.534701721497247</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.985515586903823</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.58981378993994</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.753640973780433</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.415041869050677</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.41488149058641</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>2.048732848502366</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.58981378993994</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.768930143014642</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.322686068373119</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.417351197048216</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.955389165240085</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5873440834781338</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.675092518459999</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.24194792985842</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.485721383372225</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.847302952195783</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5966197825143488</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.59991979936703</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.232384638490311</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.499509436219272</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.832224439688855</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5966197825143488</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.590356507998921</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.057094203530698</v>
+        <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.530502595547977</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.64453674099776</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5966197825143488</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.415066073039308</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.061661435522486</v>
+        <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.355028335755508</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.719293676906535</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5966197825143488</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.419633305031096</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.037403464283693</v>
+        <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.465964588396757</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.650661204611243</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5966197825143488</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.395375333792303</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.965941777685143</v>
+        <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.432301042924475</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.592664936201606</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6302833279866307</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.344111774477121</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.976114164117275</v>
+        <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.372448423720752</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.626778370315227</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6302833279866307</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.354284160909254</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.971060434691136</v>
+        <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.286204960694374</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.656222026099639</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6302833279866307</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.349230431483114</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.962836210135661</v>
+        <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.331511780093354</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.629875073784572</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5894731649773999</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.316520109122101</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.963388083168763</v>
+        <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.360544884795656</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.618813704936753</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5894731649773999</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.317071982155203</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.892660775060128</v>
+        <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.267734403344797</v>
+        <v>-3.303024231880388</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.585210589408462</v>
+        <v>1.148075267107371</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6822836464282592</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.302030962917084</v>
+        <v>2.870031453678004</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.894534250984729</v>
+        <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.312123872674224</v>
+        <v>-3.347413701209815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.569328277601292</v>
+        <v>1.132192955300201</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6378941770988316</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.277270757244028</v>
+        <v>2.845271248004948</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.889609959496452</v>
+        <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.199452654437974</v>
+        <v>-3.234742482973565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.609472473407515</v>
+        <v>1.172337151106424</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7505653953350817</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.339949196697502</v>
+        <v>2.907949687458421</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.895101255327119</v>
+        <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.087075653255301</v>
+        <v>-3.122365481790892</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.659914569711252</v>
+        <v>1.22277924741016</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7505653953350817</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.345440492528168</v>
+        <v>2.913440983289088</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.906598457095658</v>
+        <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.114856051156655</v>
+        <v>-3.150145879692245</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.660299612319249</v>
+        <v>1.223164290018158</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7227849974337286</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.340269455555896</v>
+        <v>2.908269946316816</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.744954177096312</v>
+        <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.233236723886793</v>
+        <v>-3.268526552422384</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.451303063227847</v>
+        <v>1.014167740926756</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6555671452827524</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.138294464265964</v>
+        <v>2.706294955026883</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.865103837815517</v>
+        <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.341850802330124</v>
+        <v>-3.377140630865715</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.52800709256972</v>
+        <v>1.090871770268629</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6555671452827524</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.258444124985169</v>
+        <v>2.826444615746089</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.87961686391784</v>
+        <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.306441764081981</v>
+        <v>-3.341731592617572</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.556683733971301</v>
+        <v>1.119548411670209</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6555671452827524</v>
+        <v>0.6406002813623778</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.272957151087492</v>
+        <v>2.840957641848412</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.877036305260209</v>
+        <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.26805810152383</v>
+        <v>-3.303347930059421</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.56945664033693</v>
+        <v>1.132321318035838</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6939508078409036</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.293406789964751</v>
+        <v>2.861407280725671</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.873765334105511</v>
+        <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.090941771488664</v>
+        <v>-3.126231600024255</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.637032201196298</v>
+        <v>1.199896878895206</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6939508078409036</v>
+        <v>0.678983943920529</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.290135818810053</v>
+        <v>2.858136309570973</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.874448725867424</v>
+        <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.13603401632221</v>
+        <v>-3.171323844857801</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.619678695024793</v>
+        <v>1.182543372723701</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6320547646715138</v>
+        <v>0.6170879007511392</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.253681584670332</v>
+        <v>2.821682075431252</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.868235701173838</v>
+        <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.956658595083442</v>
+        <v>-2.991948423619033</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.685215838826714</v>
+        <v>1.248080516525623</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7888315228422325</v>
+        <v>0.7738646589218579</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.341534614879178</v>
+        <v>2.909535105640098</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.849043156505428</v>
+        <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.001672808604048</v>
+        <v>-3.036962637139639</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.648017608750062</v>
+        <v>1.21088228644897</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7584826275276279</v>
+        <v>0.7435157636072532</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.304132733022005</v>
+        <v>2.872133223782925</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.854734718844374</v>
+        <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.268677318876484</v>
+        <v>-3.303967147412075</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.546907366980033</v>
+        <v>1.109772044678941</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5641195894846793</v>
+        <v>0.5491527255643047</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.193206472535182</v>
+        <v>2.761206963296102</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.853938640740875</v>
+        <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.369875100313656</v>
+        <v>-3.405164928849247</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.505632176301666</v>
+        <v>1.068496854000574</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4957107759393602</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.151365106304492</v>
+        <v>2.719365597065412</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.851538602295192</v>
+        <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.363364133699344</v>
+        <v>-3.398653962234935</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.505836524501707</v>
+        <v>1.068701202200615</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4957107759393602</v>
+        <v>0.4807439120189855</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.148965067858808</v>
+        <v>2.716965558619728</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.848063321503437</v>
+        <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.344326005992047</v>
+        <v>-3.379615834527637</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.509976494792871</v>
+        <v>1.072841172491779</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4375271646081657</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.110579620268337</v>
+        <v>2.678580111029257</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.025645190442118</v>
+        <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.375452637142665</v>
+        <v>-3.410742465678255</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.675107711271304</v>
+        <v>1.237972388970213</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4375271646081657</v>
+        <v>0.422560300687791</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.288161489207017</v>
+        <v>2.856161979967937</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.026478519428251</v>
+        <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.389319398476582</v>
+        <v>-3.424609227012173</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.670394335723871</v>
+        <v>1.233259013422779</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3996692478743427</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.266280068152857</v>
+        <v>2.834280558913777</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.032487049825177</v>
+        <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.344515226936652</v>
+        <v>-3.379805055472243</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.694324534736769</v>
+        <v>1.257189212435677</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3996692478743427</v>
+        <v>0.3847023839539681</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.272288598549783</v>
+        <v>2.840289089310703</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.930437271102377</v>
+        <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.19677225670165</v>
+        <v>-3.232062085237241</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.651371944107969</v>
+        <v>1.214236621806878</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5674766051092259</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.270923234167912</v>
+        <v>2.838923724928832</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.933230892633858</v>
+        <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.298786939232871</v>
+        <v>-3.334076767768462</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.613359692626962</v>
+        <v>1.17622437032587</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5674766051092259</v>
+        <v>0.5525097411888512</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.273716855699393</v>
+        <v>2.841717346460313</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.933893241025516</v>
+        <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.292634233180086</v>
+        <v>-3.327924061715677</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.616483123439734</v>
+        <v>1.179347801138642</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5736293111620102</v>
+        <v>0.5586624472416355</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.278070827722722</v>
+        <v>2.846071318483642</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.932973717765626</v>
+        <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.309443531330588</v>
+        <v>-3.344733359866179</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.608839880919644</v>
+        <v>1.171704558618552</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5568200130115086</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.267065725572531</v>
+        <v>2.835066216333451</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.999309271562447</v>
+        <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.247145532554466</v>
+        <v>-3.282435361090057</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.700094634226913</v>
+        <v>1.262959311925822</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5568200130115086</v>
+        <v>0.5418531490911338</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.333401279369352</v>
+        <v>2.901401770130272</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.801601273276574</v>
+        <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.281517451856905</v>
+        <v>-3.080645163424899</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.488637868220065</v>
+        <v>1.145967392706012</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5760371890237018</v>
+        <v>0.7398713412602882</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.147223586690795</v>
+        <v>2.822504687145892</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.871891505598749</v>
+        <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.116704448778058</v>
+        <v>-2.915832160346052</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.624853301773779</v>
+        <v>1.282182826259726</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7408501921025488</v>
+        <v>0.9046843443391351</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.316401620860279</v>
+        <v>2.991682721315375</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.886519241714793</v>
+        <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.214444993403032</v>
+        <v>-3.013572704971026</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.600384820039833</v>
+        <v>1.25771434452578</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7249609139695685</v>
+        <v>0.888795066206155</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.321495790096535</v>
+        <v>2.996776890551631</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.885055222539465</v>
+        <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.390782753525961</v>
+        <v>-3.189910465093956</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.528385696815333</v>
+        <v>1.18571522130128</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5486231538466391</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.214229114847448</v>
+        <v>2.889510215302545</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.883546840579393</v>
+        <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.314360707094035</v>
+        <v>-3.113488418662029</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.557446133428032</v>
+        <v>1.214775657913979</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5486231538466391</v>
+        <v>0.7124573060832255</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.212720732887377</v>
+        <v>2.888001833342473</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.883409708014829</v>
+        <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.269987575455466</v>
+        <v>-3.06911528702346</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.575058253518896</v>
+        <v>1.232387778004843</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5929962854852077</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.239207479305954</v>
+        <v>2.914488579761051</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.87780350215342</v>
+        <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.147153354568299</v>
+        <v>-2.946281066136293</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.618585736012353</v>
+        <v>1.2759152604983</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5929962854852077</v>
+        <v>0.7568304377217941</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.233601273444545</v>
+        <v>2.908882373899641</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.884185259181224</v>
+        <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.099497624007243</v>
+        <v>-2.898625335575237</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.64402978526458</v>
+        <v>1.301359309750527</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6406520160462633</v>
+        <v>0.8044861682828498</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.268576468808983</v>
+        <v>2.943857569264079</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.889077632555949</v>
+        <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.998979465508488</v>
+        <v>-2.798107177076482</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.689129422038807</v>
+        <v>1.346458946524754</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7411701745450179</v>
+        <v>0.9050043267816044</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.33377973728296</v>
+        <v>3.009060837738057</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.875832305031822</v>
+        <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.059646055910877</v>
+        <v>-2.858773767478871</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.651617458353723</v>
+        <v>1.30894698283967</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6594718578264842</v>
+        <v>0.8233060100630707</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.271515419727712</v>
+        <v>2.946796520182809</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.87993000764245</v>
+        <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.014807654302479</v>
+        <v>-2.813935365870473</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.673650521607711</v>
+        <v>1.330980046093658</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6640152907713537</v>
+        <v>0.8278494430079402</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.278339182105263</v>
+        <v>2.953620282560359</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.884090947273528</v>
+        <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.034306110544487</v>
+        <v>-2.833433822112482</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.670012078741986</v>
+        <v>1.327341603227933</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6159306494914494</v>
+        <v>0.7797648017280359</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.253649336968398</v>
+        <v>2.928930437423495</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.889970549801365</v>
+        <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.990103273458587</v>
+        <v>-2.789230985026581</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.693572816104183</v>
+        <v>1.35090234059013</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6601334865773498</v>
+        <v>0.8239676388139363</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.286050641747775</v>
+        <v>2.961331742202872</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.888380550270613</v>
+        <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.02708230112203</v>
+        <v>-2.826210012690024</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.677191205508054</v>
+        <v>1.334520729994001</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6971073883686804</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.306644983291821</v>
+        <v>2.981926083746918</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.939628315453652</v>
+        <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.868790883582758</v>
+        <v>-2.667918595150752</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.791755537706802</v>
+        <v>1.449085062192749</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6971073883686804</v>
+        <v>0.8609415406052668</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.357892748474861</v>
+        <v>3.033173848929958</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.938069020047906</v>
+        <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.661148879948282</v>
+        <v>-2.460276591516276</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.873253043754846</v>
+        <v>1.530582568240793</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9047493920031565</v>
+        <v>1.068583544239743</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.4809186552498</v>
+        <v>3.156199755704896</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.933017248286176</v>
+        <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.610116787225754</v>
+        <v>-2.409244498793748</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.888614109082127</v>
+        <v>1.545943633568074</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9557814847256845</v>
+        <v>1.119615636962271</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.506486139121586</v>
+        <v>3.181767239576683</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.950204652378881</v>
+        <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.544892606098548</v>
+        <v>-2.344020317666542</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.931891185625714</v>
+        <v>1.589220710111661</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.02100566585289</v>
+        <v>1.184839818089477</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.562808051890615</v>
+        <v>3.238089152345712</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.946165624678161</v>
+        <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.507465586027414</v>
+        <v>-2.306593297595409</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.942822965953448</v>
+        <v>1.600152490439395</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.026257203882072</v>
+        <v>1.190091356118658</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.561919947007404</v>
+        <v>3.237201047462501</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.947422417009401</v>
+        <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.527577242062123</v>
+        <v>-2.326704953630117</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.936035095870805</v>
+        <v>1.593364620356752</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.037284548879491</v>
+        <v>1.201118701116078</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.569793146337096</v>
+        <v>3.245074246792193</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.107980188030612</v>
+        <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.473832427634918</v>
+        <v>-2.272960139202912</v>
       </c>
       <c r="E1991" t="n">
-        <v>2.118090792662898</v>
+        <v>1.775420317148845</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.047347858319953</v>
+        <v>1.21118201055654</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.736388903022584</v>
+        <v>3.41167000347768</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.228093097248429</v>
+        <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.399050166609905</v>
+        <v>-2.1981778781779</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.26811660629072</v>
+        <v>1.925446130776667</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.122130119344966</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.901371168855409</v>
+        <v>3.576652269310506</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.219801073262288</v>
+        <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.372966082346097</v>
+        <v>-2.172093793914092</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.270258216010102</v>
+        <v>1.927587740496049</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.122130119344966</v>
+        <v>1.285964271581552</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.893079144869268</v>
+        <v>3.568360245324365</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.217994268846068</v>
+        <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.294834901497151</v>
+        <v>-2.093962613065145</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.29970388393346</v>
+        <v>1.957033408419407</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.19630693022865</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.935778426983259</v>
+        <v>3.611059527438355</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.235548674572859</v>
+        <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.285942440103867</v>
+        <v>-2.085070151671862</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.320815274217565</v>
+        <v>1.978144798703512</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.19630693022865</v>
+        <v>1.360141082465237</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.95333283271005</v>
+        <v>3.628613933165146</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.227403721977443</v>
+        <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.454418557073745</v>
+        <v>-2.25354626864174</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.245279874834198</v>
+        <v>1.902609399320145</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.16835909451207</v>
+        <v>1.332193246748656</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.928419178684685</v>
+        <v>3.603700279139781</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.208673419165305</v>
+        <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.756619028212162</v>
+        <v>-1.964643911637965</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.505669383566693</v>
+        <v>1.999440039309516</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.098011035141659</v>
+        <v>1.201014608914833</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.8674800402503</v>
+        <v>3.50626279362735</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.199337441662209</v>
+        <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.73389792452901</v>
+        <v>-1.941922807954812</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.505421847536858</v>
+        <v>1.999192503279682</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.098011035141659</v>
+        <v>1.201014608914833</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.858144062747205</v>
+        <v>3.496926816124254</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.358243567513378</v>
+        <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.732172881238966</v>
+        <v>-1.940197764664769</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.665017990704045</v>
+        <v>2.158788646446868</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.099736078431703</v>
+        <v>1.202739652204877</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.0180852145724</v>
+        <v>3.65686796794945</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.395321390007025</v>
+        <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.886953888017221</v>
+        <v>-2.094978771443024</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.640183410486389</v>
+        <v>2.133954066229213</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.066368404377227</v>
+        <v>1.169371978150401</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.035142432633361</v>
+        <v>3.67392518601041</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.39199674599657</v>
+        <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.879899197802047</v>
+        <v>-2.08792408122785</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.639680642562004</v>
+        <v>2.133451298304827</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.0734230945924</v>
+        <v>1.176426668365575</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.03605060275201</v>
+        <v>3.67483335612906</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.402002899641312</v>
+        <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.852947973475559</v>
+        <v>-2.060972856901362</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.660467285937341</v>
+        <v>2.154237941680164</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.08830344062012</v>
+        <v>1.191307014393294</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.054984964013384</v>
+        <v>3.693767717390433</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.586106031786271</v>
+        <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.988900981531875</v>
+        <v>-2.18986991620005</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.790189214859774</v>
+        <v>2.286782250105649</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.08830344062012</v>
+        <v>1.191307014393294</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.239088096158343</v>
+        <v>3.877870849535392</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.578222726689265</v>
+        <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.011309099336748</v>
+        <v>-2.212278034004922</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.773342662640818</v>
+        <v>2.269935697886693</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.08830344062012</v>
+        <v>1.191307014393294</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.231204791061336</v>
+        <v>3.869987544438386</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.580276726238902</v>
+        <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.159314866816147</v>
+        <v>-2.360283801484321</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.716194355198696</v>
+        <v>2.212787390444571</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.001576431756578</v>
+        <v>1.104580005529752</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.181222585292849</v>
+        <v>3.820005338669898</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.636530443960749</v>
+        <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.168755792704677</v>
+        <v>-2.369724727372851</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.768671702565131</v>
+        <v>2.265264737811006</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.12400354929997</v>
+        <v>1.227007123073144</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.310932573540731</v>
+        <v>3.94971532691778</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.63942153850605</v>
+        <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.221029400040318</v>
+        <v>-2.421998334708493</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.750653354176175</v>
+        <v>2.24724638942205</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.071729941964328</v>
+        <v>1.174733515737502</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.282459503684647</v>
+        <v>3.921242257061696</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.637533351399825</v>
+        <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.297359377641224</v>
+        <v>-2.498328312309399</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.718233176029588</v>
+        <v>2.214826211275463</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.071729941964328</v>
+        <v>1.174733515737502</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.280571316578422</v>
+        <v>3.919354069955471</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.632353581002687</v>
+        <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.409116330256525</v>
+        <v>-2.6100852649247</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.66835062458633</v>
+        <v>2.164943659832205</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9599729893490272</v>
+        <v>1.062976563122201</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.208337374612104</v>
+        <v>3.847120127989153</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.63078759121284</v>
+        <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.407275311198274</v>
+        <v>-2.608244245866449</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.667521042419783</v>
+        <v>2.164114077665658</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9612412160204956</v>
+        <v>1.06424478979367</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.207532320825138</v>
+        <v>3.846315074202186</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.643860998078758</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.539576603295827</v>
+        <v>-2.740545537964002</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.62767393244668</v>
+        <v>2.124266967692555</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9612412160204956</v>
+        <v>1.06424478979367</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.220605727691056</v>
+        <v>3.859388481068105</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.643860998078758</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.541138246110688</v>
+        <v>-2.742107180778862</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.627049275320736</v>
+        <v>2.123642310566611</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9612412160204956</v>
+        <v>1.06424478979367</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.220605727691056</v>
+        <v>3.859388481068105</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.64238503920576</v>
+        <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.56903903322016</v>
+        <v>-2.770007967888335</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.614413001603949</v>
+        <v>2.111006036849824</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9266442918775608</v>
+        <v>1.029647865650735</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.198371614332297</v>
+        <v>3.837154367709346</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.639149483182959</v>
+        <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.691565135923054</v>
+        <v>-2.892534070591229</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.56216700449999</v>
+        <v>2.058760039745865</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8041181891746669</v>
+        <v>0.907121762947841</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.12162039668776</v>
+        <v>3.760403150064809</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.705855442773463</v>
+        <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.711626457199561</v>
+        <v>-2.912595391867736</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.620848435579891</v>
+        <v>2.117441470825766</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7840568678981599</v>
+        <v>0.8870604416713339</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.176289563512359</v>
+        <v>3.815072316889408</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.84616716177531</v>
+        <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.968347275194385</v>
+        <v>-3.16931620986256</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.658471827383809</v>
+        <v>2.155064862629684</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.675642293754345</v>
+        <v>0.7786458675275191</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.251552538027918</v>
+        <v>3.890335291404966</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.91514743092095</v>
+        <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.122333692970526</v>
+        <v>-3.3233026276387</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.665857529418992</v>
+        <v>2.162450564664867</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.675642293754345</v>
+        <v>0.7786458675275191</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.320532807173557</v>
+        <v>3.959315560550606</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.901198633041071</v>
+        <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.07181178914286</v>
+        <v>-3.272780723811034</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.672117493070179</v>
+        <v>2.168710528316054</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.675642293754345</v>
+        <v>0.7786458675275191</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.306584009293678</v>
+        <v>3.945366762670727</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.913069122096485</v>
+        <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.324286943150584</v>
+        <v>-3.525255877818759</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.582997920522504</v>
+        <v>2.079590955768379</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.675642293754345</v>
+        <v>0.7786458675275191</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.318454498349092</v>
+        <v>3.957237251726141</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.914279656615428</v>
+        <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.593759745072292</v>
+        <v>-3.794728679740467</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.476419334272764</v>
+        <v>1.973012369518639</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.675642293754345</v>
+        <v>0.7786458675275191</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.319665032868036</v>
+        <v>3.958447786245085</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.91840139884275</v>
+        <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.751303816801733</v>
+        <v>-3.952272751469908</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.41752344780831</v>
+        <v>1.914116483054184</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6087404886140706</v>
+        <v>0.7117440623872446</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.283645692011193</v>
+        <v>3.922428445388242</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.91347925157894</v>
+        <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.88015436750378</v>
+        <v>-4.081123302171955</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.36106108026368</v>
+        <v>1.857654115509555</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.567747079763349</v>
+        <v>0.6707506535365231</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.254127499436949</v>
+        <v>3.892910252813998</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
-        <v>4.075683308277984</v>
+        <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.997122060142671</v>
+        <v>-4.198090994810846</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.476478059907168</v>
+        <v>1.973071095153042</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.567747079763349</v>
+        <v>0.6707506535365231</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.416331556135994</v>
+        <v>4.055114309513042</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
-        <v>4.070529946241798</v>
+        <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.081840002363625</v>
+        <v>-4.282808937031799</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.437437520982601</v>
+        <v>1.934030556228475</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4826310508353027</v>
+        <v>0.5856346246084767</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.36010857674298</v>
+        <v>3.998891330120029</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
-        <v>4.08075936381029</v>
+        <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.163774820632508</v>
+        <v>-4.364743755300682</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.41489301124354</v>
+        <v>1.911486046489413</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4726963052482225</v>
+        <v>0.5756998790213965</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.364377146959224</v>
+        <v>4.003159900336271</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
-        <v>4.089685002266192</v>
+        <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.110036647232246</v>
+        <v>-4.31100558190042</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.445313919059546</v>
+        <v>1.94190695430542</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5264344786484846</v>
+        <v>0.6294380524216586</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.405545689455283</v>
+        <v>4.044328442832331</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
-        <v>4.081837889510368</v>
+        <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.000030363755024</v>
+        <v>-4.200999298423199</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.481469319694611</v>
+        <v>1.978062354940485</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5496390505657598</v>
+        <v>0.6526426243389338</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.411621319849824</v>
+        <v>4.050404073226872</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
-        <v>4.086087900232342</v>
+        <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.856970788014098</v>
+        <v>-4.057939722682272</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.542943160712955</v>
+        <v>2.039536195958829</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5576524771557391</v>
+        <v>0.6606560509289131</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.420679386525785</v>
+        <v>4.059462139902833</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
-        <v>4.093348783114878</v>
+        <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.555524062542261</v>
+        <v>-3.756492997210435</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.670782733784227</v>
+        <v>2.1673757690301</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8590992026275763</v>
+        <v>0.9621027764007504</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.608808304691425</v>
+        <v>4.247591058068472</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
-        <v>4.094319960867589</v>
+        <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.61047925898533</v>
+        <v>-3.811448193653504</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.64977183295971</v>
+        <v>2.146364868205583</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8590992026275763</v>
+        <v>0.9621027764007504</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.609779482444135</v>
+        <v>4.248562235821183</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859302</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
-        <v>4.095162865247344</v>
+        <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-2.965143380509428</v>
+        <v>-3.760409817646984</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.908749088729826</v>
+        <v>2.167623122987947</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8590992026275763</v>
+        <v>0.9621027764007504</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.61062238682389</v>
+        <v>4.249405140200938</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.858096227715832</v>
+        <v>3.760795191693467</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.126098138708092</v>
+        <v>3.67817179326418</v>
       </c>
       <c r="D2032" t="n">
-        <v>-2.965143380509428</v>
+        <v>-3.760409817646984</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.908749088729826</v>
+        <v>2.167623122987947</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8590992026275763</v>
+        <v>0.9621027764007504</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.11916193569446</v>
+        <v>3.671235590250548</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.2%</t>
+          <t>457.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-537.6%</t>
+          <t>-497.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.5%</t>
+          <t>-142.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.7%</t>
+          <t>-131.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-127.8%</t>
+          <t>-118.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-14.3%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.964643911637965</v>
+        <v>-1.555746739780156</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.999440039309516</v>
+        <v>2.16299890805264</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.201014608914833</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.50626279362735</v>
+        <v>3.542761140705397</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.941922807954812</v>
+        <v>-1.533025636097004</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.999192503279682</v>
+        <v>2.162751372022805</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.201014608914833</v>
+        <v>1.261845187378245</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.496926816124254</v>
+        <v>3.533425163202302</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.940197764664769</v>
+        <v>-1.53130059280696</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.158788646446868</v>
+        <v>2.322347515189992</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.202739652204877</v>
+        <v>1.263570230668289</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.65686796794945</v>
+        <v>3.693366315027497</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.094978771443024</v>
+        <v>-1.686081599585215</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.133954066229213</v>
+        <v>2.297512934972336</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.169371978150401</v>
+        <v>1.230202556613813</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67392518601041</v>
+        <v>3.710423533088457</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.08792408122785</v>
+        <v>-1.679026909370042</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.133451298304827</v>
+        <v>2.297010167047951</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.176426668365575</v>
+        <v>1.237257246828987</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.67483335612906</v>
+        <v>3.711331703207107</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.060972856901362</v>
+        <v>-1.652075685043554</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.154237941680164</v>
+        <v>2.317796810423288</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.191307014393294</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.693767717390433</v>
+        <v>3.73026606446848</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.18986991620005</v>
+        <v>-1.785115609016203</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.286782250105649</v>
+        <v>2.448683972979188</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.191307014393294</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.877870849535392</v>
+        <v>3.91436919661344</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.212278034004922</v>
+        <v>-1.807523726821075</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.269935697886693</v>
+        <v>2.431837420760232</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.191307014393294</v>
+        <v>1.252137592856706</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.869987544438386</v>
+        <v>3.906485891516433</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.360283801484321</v>
+        <v>-1.955529494300474</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.212787390444571</v>
+        <v>2.37468911331811</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.104580005529752</v>
+        <v>1.165410583993165</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.820005338669898</v>
+        <v>3.856503685747946</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.369724727372851</v>
+        <v>-1.964970420189004</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.265264737811006</v>
+        <v>2.427166460684545</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.227007123073144</v>
+        <v>1.287837701536556</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.94971532691778</v>
+        <v>3.986213673995827</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.421998334708493</v>
+        <v>-2.017244027524645</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.24724638942205</v>
+        <v>2.409148112295589</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.174733515737502</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.921242257061696</v>
+        <v>3.957740604139744</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.498328312309399</v>
+        <v>-2.093574005125551</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.214826211275463</v>
+        <v>2.376727934149002</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.174733515737502</v>
+        <v>1.235564094200915</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.919354069955471</v>
+        <v>3.955852417033519</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.6100852649247</v>
+        <v>-2.205330957740852</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.164943659832205</v>
+        <v>2.326845382705744</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.062976563122201</v>
+        <v>1.123807141585614</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.847120127989153</v>
+        <v>3.8836184750672</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.608244245866449</v>
+        <v>-2.203489938682601</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.164114077665658</v>
+        <v>2.326015800539197</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.06424478979367</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.846315074202186</v>
+        <v>3.882813421280234</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.740545537964002</v>
+        <v>-2.335791230780154</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.124266967692555</v>
+        <v>2.286168690566094</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.06424478979367</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.859388481068105</v>
+        <v>3.895886828146153</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.742107180778862</v>
+        <v>-2.337352873595014</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.123642310566611</v>
+        <v>2.28554403344015</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.06424478979367</v>
+        <v>1.125075368257082</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.859388481068105</v>
+        <v>3.895886828146153</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.770007967888335</v>
+        <v>-2.365253660704487</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.111006036849824</v>
+        <v>2.272907759723363</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.029647865650735</v>
+        <v>1.090478444114147</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.837154367709346</v>
+        <v>3.873652714787394</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.892534070591229</v>
+        <v>-2.487779763407381</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.058760039745865</v>
+        <v>2.220661762619404</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.907121762947841</v>
+        <v>0.9679523414112534</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.760403150064809</v>
+        <v>3.796901497142856</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.912595391867736</v>
+        <v>-2.507841084683888</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.117441470825766</v>
+        <v>2.279343193699305</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8870604416713339</v>
+        <v>0.9478910201347464</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.815072316889408</v>
+        <v>3.851570663967456</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.16931620986256</v>
+        <v>-2.764561902678712</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.155064862629684</v>
+        <v>2.316966585503223</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7786458675275191</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.890335291404966</v>
+        <v>3.926833638483013</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.3233026276387</v>
+        <v>-2.918548320454852</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.162450564664867</v>
+        <v>2.324352287538406</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7786458675275191</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.959315560550606</v>
+        <v>3.995813907628653</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.272780723811034</v>
+        <v>-2.868026416627186</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.168710528316054</v>
+        <v>2.330612251189593</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7786458675275191</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.945366762670727</v>
+        <v>3.981865109748775</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.525255877818759</v>
+        <v>-3.15222248049829</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.079590955768379</v>
+        <v>2.228804314696566</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7786458675275191</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.957237251726141</v>
+        <v>3.993735598804188</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.794728679740467</v>
+        <v>-3.421695282419998</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.973012369518639</v>
+        <v>2.122225728446827</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7786458675275191</v>
+        <v>0.8394764459909315</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.958447786245085</v>
+        <v>3.994946133323132</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.952272751469908</v>
+        <v>-3.579239354149439</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.914116483054184</v>
+        <v>2.063329841982371</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7117440623872446</v>
+        <v>0.7725746408506571</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.922428445388242</v>
+        <v>3.958926792466289</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.081123302171955</v>
+        <v>-3.708089904851486</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.857654115509555</v>
+        <v>2.006867474437742</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6707506535365231</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.892910252813998</v>
+        <v>3.929408599892046</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.198090994810846</v>
+        <v>-3.825057597490377</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.973071095153042</v>
+        <v>2.12228445408123</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6707506535365231</v>
+        <v>0.7315812319999355</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.055114309513042</v>
+        <v>4.09161265659109</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.282808937031799</v>
+        <v>-3.909775539711331</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.934030556228475</v>
+        <v>2.083243915156663</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5856346246084767</v>
+        <v>0.6464652030718891</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.998891330120029</v>
+        <v>4.035389677198076</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.364743755300682</v>
+        <v>-3.991710357980214</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.911486046489413</v>
+        <v>2.0606994054176</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5756998790213965</v>
+        <v>0.636530457484809</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.003159900336271</v>
+        <v>4.039658247414319</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.31100558190042</v>
+        <v>-3.937972184579952</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.94190695430542</v>
+        <v>2.091120313233608</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6294380524216586</v>
+        <v>0.6902686308850711</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.044328442832331</v>
+        <v>4.080826789910379</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.200999298423199</v>
+        <v>-3.82796590110273</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.978062354940485</v>
+        <v>2.127275713868672</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6526426243389338</v>
+        <v>0.7134732028023463</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.050404073226872</v>
+        <v>4.086902420304919</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.057939722682272</v>
+        <v>-3.684906325361804</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.039536195958829</v>
+        <v>2.188749554887016</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.6606560509289131</v>
+        <v>0.7214866293923256</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.059462139902833</v>
+        <v>4.095960486980881</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.756492997210435</v>
+        <v>-3.383459599889967</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.1673757690301</v>
+        <v>2.316589127958287</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9621027764007504</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.247591058068472</v>
+        <v>4.284089405146519</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.811448193653504</v>
+        <v>-3.438414796333036</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.146364868205583</v>
+        <v>2.29557822713377</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9621027764007504</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.248562235821183</v>
+        <v>4.28506058289923</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
         <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.760409817646984</v>
+        <v>-3.387376420326516</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.167623122987947</v>
+        <v>2.316836481916134</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.9621027764007504</v>
+        <v>1.022933354864163</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.249405140200938</v>
+        <v>4.285903487278985</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.760795191693467</v>
+        <v>3.795780653496888</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.67817179326418</v>
+        <v>3.685270067976547</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.760409817646984</v>
+        <v>-3.356428093273965</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.167623122987947</v>
+        <v>2.342342406353213</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.9621027764007504</v>
+        <v>1.053881681916714</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.671235590250548</v>
+        <v>4.317599077126575</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240721.xlsx
+++ b/tame_output/ON/bt/strategyON_20240721.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>121.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-637.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-67.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-497.2%</t>
+          <t>-518.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-255.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>191.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-142.0%</t>
+          <t>-149.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-257.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-135.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-118.6%</t>
+          <t>-137.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-154.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-25.3%</t>
         </is>
       </c>
     </row>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.521528255888915</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.31510380736147</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.3412233643097508</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.919337515444933</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.756222250021468</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.20951098471054</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.3348870970804956</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.911424050784578</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.09188489725192</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.073826517474324</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.4028180825694004</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.8692460511472</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.168329227454792</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>1.049736345627417</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.3223725734757385</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.924000916837638</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.533456610093539</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.9029399075777498</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.618683357774751</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.745468961264062</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-5.942045387274216</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.7382659407202379</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.027272134955429</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.499077238970414</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.055805799297081</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.6879472083825524</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.027272134955429</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.494262671441875</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.472197673584079</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.5193845092766307</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.027272134955429</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.492256722050752</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.716469074311148</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4319346396544819</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.027272134955429</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.502515412719431</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-6.921720093547909</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.3459337971054732</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.027272134955429</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.498614977865127</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-6.969922910790253</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.3250575902635364</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.027272134955429</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.497019897920127</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.26658425260045</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.2101720294686658</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.096015270689308</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.459552992409008</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.453303960909753</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.1314578416105414</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.096015270689308</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.455526687874605</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-7.836305349652384</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.021844815208095</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.096015270689308</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.455424586553021</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-7.840791794853772</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.0210678773172206</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.100501715890697</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.455304235403618</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.200322117357775</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.1595297030207714</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.100501715890697</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.460654538701669</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.250671180811997</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.1717533084452825</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.150850779344919</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.438361120586312</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.348290458233393</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.207759268792072</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.248470056766315</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.382831304755244</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.402361957741752</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.2264943122738434</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.302541556274675</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.3532819613718</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.606620133071615</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.3026843852871464</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.430180500888664</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.282211791722049</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.640272971580089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.3116629662060997</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.530593868805701</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.226446325456263</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.56680313991264</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.266903332045699</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.457124037138253</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.285899925950153</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.741927557299183</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.3223978782527999</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.632248454524797</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.195380496265743</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-8.976379651313673</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.4233978807601915</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.632248454524797</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.188161331364147</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.080754382340119</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.4718199639447462</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.736623185551242</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.118864301974304</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.133540537940446</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.4918186363463208</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.83229867213364</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.062574799863421</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.259577331308735</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5395396250645219</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.807047049323897</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.080419502178382</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.202505559412804</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.5127205806197486</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.807047049323897</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.084409837864783</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.344177401136925</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.5708645442081384</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.807047049323897</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.082934610966041</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.29458655671209</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.5359747962733326</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.757456204899063</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.127742527785814</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.145668222240234</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.4894585961312727</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.72620661416389</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.133441148580234</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-8.919823069520824</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.3895414620072999</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.684279938576727</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.168176226968741</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.795244413183232</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.3385708549162043</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.684279938576727</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.1693153715248</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-8.848139701227518</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.3570951959718114</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.67932459248828</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.174922353339976</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.776006525939637</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.3225082216180226</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.67932459248828</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.180656057578612</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.70464013332999</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.3036989269680288</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.607958199878633</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.213738630750536</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.611181099344765</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.2761987946868465</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.607958199878633</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.203855149437628</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.343939298476368</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.1711366348388612</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.607958199878633</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.202020588938254</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.246032259799877</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.1322741343417255</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.539972450018076</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.242511723881127</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.222078718823919</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.122024211805849</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.516018909042119</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.257552354612195</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-7.958018780501123</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.02966055263848277</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.251958970719322</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.402728001444121</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.250939156996285</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.2503842631031516</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.251958970719322</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.39994096778382</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.210754858630095</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.2668016063374692</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.211774672353132</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.424395170691376</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.047354987690732</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.3315283759339711</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.048374801413769</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.52180191447575</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-6.813873765461134</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.4328452936636631</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8148935791841705</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.669815076651362</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.664207374453619</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.4898196397537098</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7219900879416346</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.722664961083924</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.531931900822732</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.5380973159530913</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.5897146143107479</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.797397732009483</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.37619356826299</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.6032077096646251</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4339762817510063</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.893655792232965</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.127193769579409</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.7157139703617159</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4339762817510063</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.906562133456624</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.232783759352514</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.5455020448532557</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.5395662715241107</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.715232209993542</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.251518661471111</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.5865524258829033</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.545162281184242</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.76041894607455</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.103578620063511</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.5258495197577755</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.5248413652756845</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.652732572931517</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.050609097809523</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.5383233424058926</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4718718430216956</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.675800300030432</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.007060691038832</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.5487820930190757</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4718718430216956</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.668839687935339</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-5.973697484560064</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.5765897299917264</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4718718430216956</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.683302042316482</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-5.865438347437542</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.6144255052999301</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4718718430216956</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.677834162775677</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-5.742147212620411</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.6612400532373592</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.3485807082045651</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.749306937676532</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.720998013716968</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.6774007110360616</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3274315093011217</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.769697435255923</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.477232571733524</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.7706875961764901</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3274315093011217</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.765478143602974</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.375469751456229</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.8135170382074239</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.314212440908693</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.775533898558447</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.125619357507154</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.906199270770756</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.314212440908693</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.768275973542149</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-4.949727265039721</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.9801552312783779</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.314212440908693</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.771875097062798</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-4.778280802017258</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>1.062061322541917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.1427659778862299</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.88807048093083</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.703991236278918</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>1.09079762645355</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.06847641214789063</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.93166469799013</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.640355494044984</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.120946724401441</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.004840669913956097</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.974540944384808</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.528928734719064</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.146711686915604</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.004840669913956097</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.955735203168604</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.288498237914204</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.244626962262426</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.2355898268909042</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.101736577876397</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.216255669743009</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.277453303365724</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.2355898268909042</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.105665891711217</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.163257347461621</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.299331216195619</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.290926085892843</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.139546231029721</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.054452461981894</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.339851241607503</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.290926085892843</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.136544302249714</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-3.834431663944883</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.429438597832922</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.4321459309608233</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.222855246301116</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.701563974881605</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.498479856260057</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.4321459309608233</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.23874942910294</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.581390891517106</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.547694934046158</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.5523190143253223</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.311999123561941</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.436718746417369</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.615651894647493</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.6969911594250597</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.408890513183223</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.496593573775061</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.577739455105842</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.6371163320673676</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.359003108170034</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.376773342864224</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.640956716704385</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.6371163320673676</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.374292277404243</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.37924304932603</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.547613033442104</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.6346466256055614</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.2804546528496</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.44761323565004</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.439526820397802</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6439223246417763</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.205281933756631</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.461401288497086</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.424448307890874</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6439223246417763</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.195718642388522</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.492394447825792</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.236760609199779</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6439223246417763</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>3.020428207428909</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.316920188033322</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.311517545108555</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6439223246417763</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>3.024995439420697</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.427856440674571</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.242885072813262</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6439223246417763</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>3.000737468181904</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.394192895202289</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.184888804403625</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6775858701140582</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.949473908866723</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.334340275998566</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.219002238517246</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6775858701140582</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.959646295298855</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.248096812972189</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.248445894301657</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6775858701140582</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.954592565872715</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.293403632371168</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.222098941986591</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.6367757071048274</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.921882243511702</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.32243673707347</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.211037573138772</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.6367757071048274</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.922434116544804</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.229626255622611</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.177434457610481</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.7295861885556868</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.907393097306685</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.274015724952038</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.161552145803311</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.6851967192262591</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.88263289163363</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.161344506715788</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.201696341609534</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.7978679374625093</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.945311331087103</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.048967505533116</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.252138437913271</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.7978679374625093</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.95080262691777</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.076747903434469</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.252523480521268</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.7700875395611562</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.945631589945497</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.268526552422384</v>
+        <v>-3.195128576164607</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.014167740926756</v>
+        <v>1.043526931429866</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.70286968741018</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.706294955026883</v>
+        <v>2.743656598655565</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.377140630865715</v>
+        <v>-3.303742654607938</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.090871770268629</v>
+        <v>1.120230960771739</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.70286968741018</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.826444615746089</v>
+        <v>2.86380625937477</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.341731592617572</v>
+        <v>-3.268333616359795</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.119548411670209</v>
+        <v>1.14890760217332</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6406002813623778</v>
+        <v>0.70286968741018</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.840957641848412</v>
+        <v>2.878319285477093</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.303347930059421</v>
+        <v>-3.229949953801644</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.132321318035838</v>
+        <v>1.161680508538949</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.678983943920529</v>
+        <v>0.7412533499683311</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.861407280725671</v>
+        <v>2.898768924354353</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.126231600024255</v>
+        <v>-3.052833623766478</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.199896878895206</v>
+        <v>1.229256069398317</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.678983943920529</v>
+        <v>0.7412533499683311</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.858136309570973</v>
+        <v>2.895497953199655</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.171323844857801</v>
+        <v>-3.097925868600024</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.182543372723701</v>
+        <v>1.211902563226812</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6170879007511392</v>
+        <v>0.6793573067989414</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.821682075431252</v>
+        <v>2.859043719059934</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.991948423619033</v>
+        <v>-2.918550447361256</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.248080516525623</v>
+        <v>1.277439707028733</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7738646589218579</v>
+        <v>0.83613406496966</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.909535105640098</v>
+        <v>2.946896749268779</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.036962637139639</v>
+        <v>-2.963564660881862</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.21088228644897</v>
+        <v>1.240241476952081</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7435157636072532</v>
+        <v>0.8057851696550554</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.872133223782925</v>
+        <v>2.909494867411606</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.303967147412075</v>
+        <v>-3.230569171154298</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.109772044678941</v>
+        <v>1.139131235182052</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5491527255643047</v>
+        <v>0.6114221316121069</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.761206963296102</v>
+        <v>2.798568606924783</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.405164928849247</v>
+        <v>-3.331766952591471</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.068496854000574</v>
+        <v>1.097856044503684</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.5430133180667878</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.719365597065412</v>
+        <v>2.756727240694093</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.398653962234935</v>
+        <v>-3.325255985977158</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.068701202200615</v>
+        <v>1.098060392703726</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4807439120189855</v>
+        <v>0.5430133180667878</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.716965558619728</v>
+        <v>2.75432720224841</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.379615834527637</v>
+        <v>-3.306217858269861</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.072841172491779</v>
+        <v>1.10220036299489</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.422560300687791</v>
+        <v>0.4848297067355932</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.678580111029257</v>
+        <v>2.715941754657938</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.410742465678255</v>
+        <v>-3.337344489420479</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.237972388970213</v>
+        <v>1.267331579473324</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.422560300687791</v>
+        <v>0.4848297067355932</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.856161979967937</v>
+        <v>2.893523623596618</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.424609227012173</v>
+        <v>-3.351211250754396</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.233259013422779</v>
+        <v>1.26261820392589</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.4469717900017703</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.834280558913777</v>
+        <v>2.871642202542458</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.379805055472243</v>
+        <v>-3.306407079214466</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.257189212435677</v>
+        <v>1.286548402938788</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3847023839539681</v>
+        <v>0.4469717900017703</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.840289089310703</v>
+        <v>2.877650732939384</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.232062085237241</v>
+        <v>-3.397981452485798</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.214236621806878</v>
+        <v>1.147868874907455</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4323179500130782</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.838923724928832</v>
+        <v>2.766808650223368</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.334076767768462</v>
+        <v>-3.499996135017019</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.17622437032587</v>
+        <v>1.109856623426447</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5525097411888512</v>
+        <v>0.4323179500130782</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.841717346460313</v>
+        <v>2.769602271754849</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.327924061715677</v>
+        <v>-3.493843428964234</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.179347801138642</v>
+        <v>1.112980054239219</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5586624472416355</v>
+        <v>0.4384706560658624</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.846071318483642</v>
+        <v>2.773956243778178</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.344733359866179</v>
+        <v>-3.510652727114736</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.171704558618552</v>
+        <v>1.105336811719129</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4216613579153608</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.835066216333451</v>
+        <v>2.762951141627988</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.282435361090057</v>
+        <v>-3.448354728338614</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.262959311925822</v>
+        <v>1.196591565026399</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5418531490911338</v>
+        <v>0.4216613579153608</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.901401770130272</v>
+        <v>2.829286695424808</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.080645163424899</v>
+        <v>-3.246564530673456</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.145967392706012</v>
+        <v>1.079599645806589</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7398713412602882</v>
+        <v>0.6196795500845151</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.822504687145892</v>
+        <v>2.750389612440428</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.915832160346052</v>
+        <v>-3.081751527594609</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.282182826259726</v>
+        <v>1.215815079360303</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9046843443391351</v>
+        <v>0.7844925531633621</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.991682721315375</v>
+        <v>2.919567646609911</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.013572704971026</v>
+        <v>-3.179492072219583</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.25771434452578</v>
+        <v>1.191346597626357</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.888795066206155</v>
+        <v>0.7686032750303819</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.996776890551631</v>
+        <v>2.924661815846167</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.189910465093956</v>
+        <v>-3.355829832342513</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.18571522130128</v>
+        <v>1.119347474401857</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.5922655149074525</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.889510215302545</v>
+        <v>2.817395140597081</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.113488418662029</v>
+        <v>-3.279407785910586</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.214775657913979</v>
+        <v>1.148407911014556</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7124573060832255</v>
+        <v>0.5922655149074525</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.888001833342473</v>
+        <v>2.81588675863701</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.06911528702346</v>
+        <v>-3.235034654272017</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.232387778004843</v>
+        <v>1.16602003110542</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6366386465460211</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.914488579761051</v>
+        <v>2.842373505055587</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.946281066136293</v>
+        <v>-3.11220043338485</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.2759152604983</v>
+        <v>1.209547513598877</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7568304377217941</v>
+        <v>0.6366386465460211</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.908882373899641</v>
+        <v>2.836767299194177</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.898625335575237</v>
+        <v>-3.064544702823794</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.301359309750527</v>
+        <v>1.234991562851104</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8044861682828498</v>
+        <v>0.6842943771070767</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.943857569264079</v>
+        <v>2.871742494558616</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.798107177076482</v>
+        <v>-2.96402654432504</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.346458946524754</v>
+        <v>1.280091199625331</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9050043267816044</v>
+        <v>0.7848125356058313</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.009060837738057</v>
+        <v>2.936945763032593</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.858773767478871</v>
+        <v>-3.024693134727429</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.30894698283967</v>
+        <v>1.242579235940247</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8233060100630707</v>
+        <v>0.7031142188872976</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.946796520182809</v>
+        <v>2.874681445477345</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.813935365870473</v>
+        <v>-2.979854733119031</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.330980046093658</v>
+        <v>1.264612299194235</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8278494430079402</v>
+        <v>0.7076576518321671</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.953620282560359</v>
+        <v>2.881505207854895</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.833433822112482</v>
+        <v>-2.999353189361039</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.327341603227933</v>
+        <v>1.26097385632851</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7797648017280359</v>
+        <v>0.6595730105522628</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.928930437423495</v>
+        <v>2.856815362718031</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.789230985026581</v>
+        <v>-2.955150352275139</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.35090234059013</v>
+        <v>1.284534593690707</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8239676388139363</v>
+        <v>0.7037758476381633</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.961331742202872</v>
+        <v>2.889216667497408</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.826210012690024</v>
+        <v>-2.992129379938582</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.334520729994001</v>
+        <v>1.268152983094577</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.7407497494294938</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.981926083746918</v>
+        <v>2.909811009041454</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.667918595150752</v>
+        <v>-2.83383796239931</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.449085062192749</v>
+        <v>1.382717315293326</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8609415406052668</v>
+        <v>0.7407497494294938</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.033173848929958</v>
+        <v>2.961058774224494</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.460276591516276</v>
+        <v>-2.626195958764833</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.530582568240793</v>
+        <v>1.46421482134137</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.068583544239743</v>
+        <v>0.9483917530639699</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.156199755704896</v>
+        <v>3.084084680999433</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.409244498793748</v>
+        <v>-2.575163866042305</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.545943633568074</v>
+        <v>1.479575886668651</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.119615636962271</v>
+        <v>0.9994238457864979</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.181767239576683</v>
+        <v>3.109652164871219</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.344020317666542</v>
+        <v>-2.5099396849151</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.589220710111661</v>
+        <v>1.522852963212238</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.184839818089477</v>
+        <v>1.064648026913704</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.238089152345712</v>
+        <v>3.165974077640247</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.306593297595409</v>
+        <v>-2.472512664843966</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.600152490439395</v>
+        <v>1.533784743539972</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.190091356118658</v>
+        <v>1.069899564942885</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.237201047462501</v>
+        <v>3.165085972757037</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.326704953630117</v>
+        <v>-2.492624320878674</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.593364620356752</v>
+        <v>1.526996873457329</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.201118701116078</v>
+        <v>1.080926909940304</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.245074246792193</v>
+        <v>3.172959172086729</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.272960139202912</v>
+        <v>-2.43887950645147</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.775420317148845</v>
+        <v>1.709052570249421</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.21118201055654</v>
+        <v>1.090990219380767</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.41167000347768</v>
+        <v>3.339554928772217</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.1981778781779</v>
+        <v>-2.364097245426457</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.925446130776667</v>
+        <v>1.859078383877244</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.285964271581552</v>
+        <v>1.165772480405779</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.576652269310506</v>
+        <v>3.504537194605041</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.172093793914092</v>
+        <v>-2.338013161162649</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.927587740496049</v>
+        <v>1.861219993596626</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.285964271581552</v>
+        <v>1.165772480405779</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.568360245324365</v>
+        <v>3.4962451706189</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.093962613065145</v>
+        <v>-2.259881980313702</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.957033408419407</v>
+        <v>1.890665661519984</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.360141082465237</v>
+        <v>1.239949291289464</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.611059527438355</v>
+        <v>3.538944452732891</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.085070151671862</v>
+        <v>-2.250989518920419</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.978144798703512</v>
+        <v>1.911777051804089</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.360141082465237</v>
+        <v>1.239949291289464</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.628613933165146</v>
+        <v>3.556498858459682</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.25354626864174</v>
+        <v>-2.419465635890297</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.902609399320145</v>
+        <v>1.836241652420722</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.332193246748656</v>
+        <v>1.212001455572883</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.603700279139781</v>
+        <v>3.531585204434318</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.555746739780156</v>
+        <v>-1.721666107028714</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.16299890805264</v>
+        <v>2.096631161153216</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.261845187378245</v>
+        <v>1.141653396202472</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.542761140705397</v>
+        <v>3.470646065999933</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.533025636097004</v>
+        <v>-1.698945003345561</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.162751372022805</v>
+        <v>2.096383625123382</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.261845187378245</v>
+        <v>1.141653396202472</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533425163202302</v>
+        <v>3.461310088496838</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.53130059280696</v>
+        <v>-1.697219960055518</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.322347515189992</v>
+        <v>2.255979768290569</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.263570230668289</v>
+        <v>1.143378439492516</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.693366315027497</v>
+        <v>3.621251240322033</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.686081599585215</v>
+        <v>-1.852000966833773</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.297512934972336</v>
+        <v>2.231145188072913</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.230202556613813</v>
+        <v>1.11001076543804</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.710423533088457</v>
+        <v>3.638308458382994</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.679026909370042</v>
+        <v>-1.844946276618599</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.297010167047951</v>
+        <v>2.230642420148528</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.237257246828987</v>
+        <v>1.117065455653214</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.711331703207107</v>
+        <v>3.639216628501643</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.652075685043554</v>
+        <v>-1.817995052292111</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.317796810423288</v>
+        <v>2.251429063523865</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.252137592856706</v>
+        <v>1.131945801680933</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.73026606446848</v>
+        <v>3.658150989763016</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.785115609016203</v>
+        <v>-1.953948060348427</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.448683972979188</v>
+        <v>2.381150992446298</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.252137592856706</v>
+        <v>1.131945801680933</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.91436919661344</v>
+        <v>3.842254121907976</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.807523726821075</v>
+        <v>-1.976356178153299</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.431837420760232</v>
+        <v>2.364304440227342</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.252137592856706</v>
+        <v>1.131945801680933</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.906485891516433</v>
+        <v>3.834370816810969</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.955529494300474</v>
+        <v>-2.124361945632699</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.37468911331811</v>
+        <v>2.30715613278522</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.165410583993165</v>
+        <v>1.045218792817391</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.856503685747946</v>
+        <v>3.784388611042482</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.964970420189004</v>
+        <v>-2.133802871521229</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.427166460684545</v>
+        <v>2.359633480151655</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.287837701536556</v>
+        <v>1.167645910360783</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.986213673995827</v>
+        <v>3.914098599290364</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.017244027524645</v>
+        <v>-2.18607647885687</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.409148112295589</v>
+        <v>2.341615131762699</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.235564094200915</v>
+        <v>1.115372303025142</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.957740604139744</v>
+        <v>3.88562552943428</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.093574005125551</v>
+        <v>-2.262406456457776</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.376727934149002</v>
+        <v>2.309194953616112</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.235564094200915</v>
+        <v>1.115372303025142</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.955852417033519</v>
+        <v>3.883737342328055</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.205330957740852</v>
+        <v>-2.374163409073077</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.326845382705744</v>
+        <v>2.259312402172854</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.123807141585614</v>
+        <v>1.003615350409841</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.8836184750672</v>
+        <v>3.811503400361737</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.203489938682601</v>
+        <v>-2.372322390014826</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.326015800539197</v>
+        <v>2.258482820006307</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.125075368257082</v>
+        <v>1.004883577081309</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.882813421280234</v>
+        <v>3.81069834657477</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.335791230780154</v>
+        <v>-2.504623682112379</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.286168690566094</v>
+        <v>2.218635710033204</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.125075368257082</v>
+        <v>1.004883577081309</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.895886828146153</v>
+        <v>3.823771753440689</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.337352873595014</v>
+        <v>-2.506185324927239</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.28554403344015</v>
+        <v>2.21801105290726</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.125075368257082</v>
+        <v>1.004883577081309</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.895886828146153</v>
+        <v>3.823771753440689</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.365253660704487</v>
+        <v>-2.534086112036712</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.272907759723363</v>
+        <v>2.205374779190473</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.090478444114147</v>
+        <v>0.9702866529383741</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.873652714787394</v>
+        <v>3.80153764008193</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.487779763407381</v>
+        <v>-2.656612214739606</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.220661762619404</v>
+        <v>2.153128782086514</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9679523414112534</v>
+        <v>0.8477605502354802</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.796901497142856</v>
+        <v>3.724786422437392</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.507841084683888</v>
+        <v>-2.676673536016113</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.279343193699305</v>
+        <v>2.211810213166415</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9478910201347464</v>
+        <v>0.8276992289589733</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.851570663967456</v>
+        <v>3.779455589261992</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.764561902678712</v>
+        <v>-2.933394354010937</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.316966585503223</v>
+        <v>2.249433604970332</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7192846548151585</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.926833638483013</v>
+        <v>3.85471856377755</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.918548320454852</v>
+        <v>-3.087380771787077</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.324352287538406</v>
+        <v>2.256819307005516</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7192846548151585</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.995813907628653</v>
+        <v>3.92369883292319</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.868026416627186</v>
+        <v>-3.036858867959412</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.330612251189593</v>
+        <v>2.263079270656704</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7192846548151585</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.981865109748775</v>
+        <v>3.909750035043311</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.15222248049829</v>
+        <v>-3.289334021967136</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.228804314696566</v>
+        <v>2.173959698109027</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7192846548151585</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.993735598804188</v>
+        <v>3.921620524098724</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.421695282419998</v>
+        <v>-3.558806823888844</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.122225728446827</v>
+        <v>2.067381111859288</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8394764459909315</v>
+        <v>0.7192846548151585</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.994946133323132</v>
+        <v>3.922831058617668</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.579239354149439</v>
+        <v>-3.716350895618285</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.063329841982371</v>
+        <v>2.008485225394833</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7725746408506571</v>
+        <v>0.652382849674884</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.958926792466289</v>
+        <v>3.886811717760825</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.708089904851486</v>
+        <v>-3.845201446320332</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.006867474437742</v>
+        <v>1.952022857850204</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6113894408241625</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.929408599892046</v>
+        <v>3.857293525186582</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.825057597490377</v>
+        <v>-3.962169138959223</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.12228445408123</v>
+        <v>2.067439837493692</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7315812319999355</v>
+        <v>0.6113894408241625</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.09161265659109</v>
+        <v>4.019497581885625</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.909775539711331</v>
+        <v>-4.046887081180176</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.083243915156663</v>
+        <v>2.028399298569124</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6464652030718891</v>
+        <v>0.5262734118961161</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.035389677198076</v>
+        <v>3.963274602492612</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.991710357980214</v>
+        <v>-4.12882189944906</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.0606994054176</v>
+        <v>2.005854788830062</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.636530457484809</v>
+        <v>0.5163386663090359</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.039658247414319</v>
+        <v>3.967543172708855</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.937972184579952</v>
+        <v>-4.075083726048797</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.091120313233608</v>
+        <v>2.03627569664607</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6902686308850711</v>
+        <v>0.570076839709298</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.080826789910379</v>
+        <v>4.008711715204915</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.82796590110273</v>
+        <v>-3.965077442571576</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.127275713868672</v>
+        <v>2.072431097281133</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7134732028023463</v>
+        <v>0.5932814116265732</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.086902420304919</v>
+        <v>4.014787345599455</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.684906325361804</v>
+        <v>-3.82201786683065</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.188749554887016</v>
+        <v>2.133904938299478</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7214866293923256</v>
+        <v>0.6012948382165525</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.095960486980881</v>
+        <v>4.023845412275417</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.383459599889967</v>
+        <v>-3.520571141358813</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.316589127958287</v>
+        <v>2.261744511370749</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9027415636883898</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.284089405146519</v>
+        <v>4.211974330441056</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.438414796333036</v>
+        <v>-3.575526337801882</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.29557822713377</v>
+        <v>2.240733610546232</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9027415636883898</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.28506058289923</v>
+        <v>4.212945508193766</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.821198342859298</v>
       </c>
       <c r="C2031" t="n">
         <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.387376420326516</v>
+        <v>-3.524487961795362</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.316836481916134</v>
+        <v>2.261991865328596</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.022933354864163</v>
+        <v>0.9027415636883898</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.285903487278985</v>
+        <v>4.213788412573521</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.795780653496888</v>
+        <v>3.837192964374161</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.685270067976547</v>
+        <v>3.691181573234633</v>
       </c>
       <c r="D2032" t="n">
-        <v>-3.356428093273965</v>
+        <v>-3.56641619018274</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.342342406353213</v>
+        <v>2.26425867284779</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.053881681916714</v>
+        <v>0.8608133353010116</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.317599077126575</v>
+        <v>4.20766957441524</v>
       </c>
     </row>
   </sheetData>
